--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EA8C5A0-EB54-4CDC-825F-86DAB36DF9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8AB8DA2-4765-4F48-A980-E281802CDD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="03.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="97">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -276,13 +276,74 @@
   </si>
   <si>
     <t>G FEITOZA DA SILVA LTDA ME CPF- 47728240000170</t>
+  </si>
+  <si>
+    <t>LUIZ GUSTAVO PILOTO CPF- 02111467812</t>
+  </si>
+  <si>
+    <t>22/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSM SOLUCOES LTDA                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINOVALDO SOARES CRISTAL                   </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SACOLAO JL LTDA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO BUENO SILVA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATIMA APARECIDA DE ANDRADE                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHEL HENRIQUE PEREIRA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATO MEDEIROS SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINE MIQUELOTTI GONCALVES DE CARVALHO    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNALDO FRANCISCO SOARES                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE CARLOS MARCELINO CALIXTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OI SERV FESTA LTDA ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANICE TEREZINHA FAVACHO VENDAS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSAENE SANTOS ANDRADE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">N L MOVEIS PLANEJADOS LTDA ME                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE DE FRANCA LIMA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIZZARIA LANCHONETE SEM LIMITE LTDA EPP      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO HENRIQUE CARNEIRO                      </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +379,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -547,7 +614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,7 +689,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -665,7 +731,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -675,13 +740,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -691,7 +752,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -704,8 +764,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1105,10 +1168,10 @@
       <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="46" t="s">
+      <c r="I2" s="45" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1122,22 +1185,22 @@
       <c r="C3" s="27">
         <v>45964</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="24">
         <v>135123173</v>
       </c>
       <c r="E3" s="18">
         <v>3450123072</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="H3" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1151,22 +1214,22 @@
       <c r="C4" s="27">
         <v>45964</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="24">
         <v>135105244</v>
       </c>
       <c r="E4" s="18">
         <v>3450121290</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="12" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="46">
+      <c r="I4" s="45">
         <v>45955</v>
       </c>
     </row>
@@ -1180,22 +1243,22 @@
       <c r="C5" s="27">
         <v>45964</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="24">
         <v>135133421</v>
       </c>
       <c r="E5" s="18">
         <v>3450123743</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="12" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1209,22 +1272,22 @@
       <c r="C6" s="27">
         <v>45964</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="24">
         <v>135140502</v>
       </c>
       <c r="E6" s="18">
         <v>3450124568</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1238,22 +1301,22 @@
       <c r="C7" s="27">
         <v>45964</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="24">
         <v>135137538</v>
       </c>
       <c r="E7" s="18">
         <v>3450124260</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="12" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="49" t="s">
+      <c r="H7" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1267,22 +1330,22 @@
       <c r="C8" s="27">
         <v>45964</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="24">
         <v>135133617</v>
       </c>
       <c r="E8" s="18">
         <v>3450123820</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="49" t="s">
+      <c r="H8" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1296,22 +1359,22 @@
       <c r="C9" s="27">
         <v>45964</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="24">
         <v>135133236</v>
       </c>
       <c r="E9" s="18">
         <v>3450123699</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1325,22 +1388,22 @@
       <c r="C10" s="27">
         <v>45964</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="24">
         <v>135155674</v>
       </c>
       <c r="E10" s="18">
         <v>3450125998</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1354,22 +1417,22 @@
       <c r="C11" s="27">
         <v>45964</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="24">
         <v>135156059</v>
       </c>
       <c r="E11" s="18">
         <v>3450126031</v>
       </c>
-      <c r="F11" s="51" t="s">
+      <c r="F11" s="12" t="s">
         <v>36</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1383,22 +1446,22 @@
       <c r="C12" s="27">
         <v>45964</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="24">
         <v>135155268</v>
       </c>
       <c r="E12" s="18">
         <v>3450125965</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="12" t="s">
         <v>38</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="H12" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1412,22 +1475,22 @@
       <c r="C13" s="27">
         <v>45964</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="24">
         <v>135156088</v>
       </c>
       <c r="E13" s="18">
         <v>3450126053</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="47" t="s">
+      <c r="H13" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1441,22 +1504,22 @@
       <c r="C14" s="27">
         <v>45964</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="24">
         <v>135162327</v>
       </c>
       <c r="E14" s="18">
         <v>3450126801</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="12" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="47" t="s">
+      <c r="H14" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1470,22 +1533,22 @@
       <c r="C15" s="27">
         <v>45964</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="24">
         <v>135163700</v>
       </c>
       <c r="E15" s="18">
         <v>3450126977</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="47" t="s">
+      <c r="H15" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1499,22 +1562,22 @@
       <c r="C16" s="27">
         <v>45964</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="24">
         <v>135154363</v>
       </c>
       <c r="E16" s="18">
         <v>3450125790</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1528,22 +1591,22 @@
       <c r="C17" s="27">
         <v>45964</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="24">
         <v>135164544</v>
       </c>
       <c r="E17" s="18">
         <v>3450126185</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="47" t="s">
+      <c r="H17" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1557,22 +1620,22 @@
       <c r="C18" s="27">
         <v>45964</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="24">
         <v>135159061</v>
       </c>
       <c r="E18" s="18">
         <v>3450126427</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="47" t="s">
+      <c r="H18" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1586,22 +1649,22 @@
       <c r="C19" s="27">
         <v>45964</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="24">
         <v>135154636</v>
       </c>
       <c r="E19" s="18">
         <v>3450125833</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="47" t="s">
+      <c r="H19" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1615,22 +1678,22 @@
       <c r="C20" s="27">
         <v>45964</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="24">
         <v>135146609</v>
       </c>
       <c r="E20" s="18">
         <v>3450125030</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="47" t="s">
+      <c r="H20" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="46">
+      <c r="I20" s="45">
         <v>45972</v>
       </c>
     </row>
@@ -1644,22 +1707,22 @@
       <c r="C21" s="27">
         <v>45964</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="24">
         <v>135174779</v>
       </c>
       <c r="E21" s="18">
         <v>3450127880</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="48" t="s">
+      <c r="H21" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="55">
         <v>45960</v>
       </c>
     </row>
@@ -1673,22 +1736,22 @@
       <c r="C22" s="27">
         <v>45964</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="24">
         <v>135129415</v>
       </c>
       <c r="E22" s="18">
         <v>3450123336</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="56" t="s">
+      <c r="G22" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="46">
+      <c r="I22" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1702,22 +1765,22 @@
       <c r="C23" s="27">
         <v>45964</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="24">
         <v>135171249</v>
       </c>
       <c r="E23" s="18">
         <v>3450127439</v>
       </c>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="56" t="s">
+      <c r="G23" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="46">
+      <c r="I23" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1731,22 +1794,22 @@
       <c r="C24" s="27">
         <v>45964</v>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="24">
         <v>135168476</v>
       </c>
       <c r="E24" s="18">
         <v>3450127153</v>
       </c>
-      <c r="F24" s="57" t="s">
+      <c r="F24" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="56" t="s">
+      <c r="G24" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="46">
+      <c r="I24" s="45">
         <v>45960</v>
       </c>
     </row>
@@ -1760,22 +1823,22 @@
       <c r="C25" s="27">
         <v>45964</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="24">
         <v>135176940</v>
       </c>
       <c r="E25" s="18">
         <v>3450128000</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="56" t="s">
+      <c r="G25" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="45">
         <v>45960</v>
       </c>
     </row>
@@ -1789,22 +1852,22 @@
       <c r="C26" s="27">
         <v>45964</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="24">
         <v>135180725</v>
       </c>
       <c r="E26" s="18">
         <v>3450128418</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="56" t="s">
+      <c r="G26" s="53" t="s">
         <v>13</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="46">
+      <c r="I26" s="45">
         <v>45964</v>
       </c>
     </row>
@@ -1818,22 +1881,22 @@
       <c r="C27" s="27">
         <v>45964</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="24">
         <v>135193358</v>
       </c>
       <c r="E27" s="18">
         <v>3450129485</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="56" t="s">
+      <c r="G27" s="53" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="46">
+      <c r="I27" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1847,22 +1910,22 @@
       <c r="C28" s="27">
         <v>45964</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="24">
         <v>135191401</v>
       </c>
       <c r="E28" s="18">
         <v>3450129166</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="56" t="s">
+      <c r="G28" s="53" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="46">
+      <c r="I28" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1876,22 +1939,22 @@
       <c r="C29" s="27">
         <v>45964</v>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="24">
         <v>135200685</v>
       </c>
       <c r="E29" s="18">
         <v>3450130376</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="56" t="s">
+      <c r="G29" s="53" t="s">
         <v>32</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1905,22 +1968,22 @@
       <c r="C30" s="27">
         <v>45964</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="24">
         <v>135133426</v>
       </c>
       <c r="E30" s="18">
         <v>3450123754</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="56" t="s">
+      <c r="G30" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="46">
+      <c r="I30" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1934,22 +1997,22 @@
       <c r="C31" s="27">
         <v>45964</v>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="24">
         <v>135139336</v>
       </c>
       <c r="E31" s="18">
         <v>3450124425</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="56" t="s">
+      <c r="G31" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="45">
         <v>45958</v>
       </c>
     </row>
@@ -1963,22 +2026,22 @@
       <c r="C32" s="27">
         <v>45964</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="24">
         <v>135110534</v>
       </c>
       <c r="E32" s="18">
         <v>3450120290</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="56" t="s">
+      <c r="G32" s="53" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="I32" s="46">
+      <c r="I32" s="45">
         <v>45954</v>
       </c>
     </row>
@@ -1992,22 +2055,22 @@
       <c r="C33" s="27">
         <v>45964</v>
       </c>
-      <c r="D33" s="55">
+      <c r="D33" s="24">
         <v>135100251</v>
       </c>
       <c r="E33" s="18">
         <v>3450121004</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="G33" s="56" t="s">
+      <c r="G33" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2021,22 +2084,22 @@
       <c r="C34" s="27">
         <v>45964</v>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="24">
         <v>135116743</v>
       </c>
       <c r="E34" s="18">
         <v>3450122313</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="56" t="s">
+      <c r="G34" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="46">
+      <c r="I34" s="45">
         <v>45957</v>
       </c>
     </row>
@@ -2050,22 +2113,22 @@
       <c r="C35" s="27">
         <v>45964</v>
       </c>
-      <c r="D35" s="55">
+      <c r="D35" s="24">
         <v>135111233</v>
       </c>
       <c r="E35" s="18">
         <v>3450121642</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="56" t="s">
+      <c r="G35" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="46">
+      <c r="I35" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2076,17 +2139,17 @@
       <c r="D36" s="24"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="47"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="46"/>
       <c r="I36" s="26"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="54"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="52"/>
       <c r="G37" s="20"/>
       <c r="H37" s="9"/>
       <c r="I37" s="26"/>
@@ -2349,13 +2412,13 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="46">
+      <c r="A2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="45">
         <v>45964</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="45">
         <v>45965</v>
       </c>
       <c r="D2" s="24" t="s">
@@ -2364,244 +2427,536 @@
       <c r="E2" s="18">
         <v>3450132246</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="26"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="26"/>
+      <c r="B3" s="58">
+        <v>45964</v>
+      </c>
+      <c r="C3" s="59">
+        <v>45965</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450131520</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D4" s="61">
+        <v>135057851</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450117429</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="58">
+        <v>45952</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="B5" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C5" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D5" s="61">
+        <v>135051461</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450116714</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="7">
+        <v>45957</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C6" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D6" s="61">
+        <v>135051444</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450116703</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C7" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D7" s="61">
+        <v>135043044</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450115746</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C8" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D8" s="61">
+        <v>135044605</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450115856</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C9" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D9" s="61">
+        <v>135048417</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450116197</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C10" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D10" s="61">
+        <v>135049114</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450116351</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C11" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D11" s="61">
+        <v>135049373</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450116373</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C12" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D12" s="61">
+        <v>135051429</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450116681</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C13" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D13" s="61">
+        <v>135051570</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450116725</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C14" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D14" s="61">
+        <v>135056953</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450117253</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C15" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D15" s="61">
+        <v>135057252</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450117352</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C16" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D16" s="61">
+        <v>135057776</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450117418</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="B17" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C17" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D17" s="61">
+        <v>135059630</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450117649</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C18" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D18" s="61">
+        <v>135059784</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450117682</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C19" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D19" s="61">
+        <v>135061235</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450117759</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45952</v>
+      </c>
+      <c r="C20" s="27">
+        <v>45965</v>
+      </c>
+      <c r="D20" s="61">
+        <v>135055840</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450117110</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="7">
+        <v>45952</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -2666,7 +3021,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="12"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="31"/>
+      <c r="H26" s="30"/>
       <c r="I26" s="26"/>
     </row>
     <row r="27" spans="1:9">
@@ -2990,7 +3345,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3046,7 +3401,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4240,7 +4595,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4273,8 +4628,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="22"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="26"/>
@@ -4804,7 +5159,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4820,8 +5175,8 @@
       <c r="D2" s="24"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="37"/>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9">
@@ -4833,8 +5188,8 @@
       <c r="D3" s="24"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="37"/>
       <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9">
@@ -4846,8 +5201,8 @@
       <c r="D4" s="24"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9">
@@ -4859,8 +5214,8 @@
       <c r="D5" s="24"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9">
@@ -4872,8 +5227,8 @@
       <c r="D6" s="24"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9">
@@ -4885,8 +5240,8 @@
       <c r="D7" s="24"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9">
@@ -4898,8 +5253,8 @@
       <c r="D8" s="24"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9">
@@ -4911,8 +5266,8 @@
       <c r="D9" s="24"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:9">
@@ -4924,8 +5279,8 @@
       <c r="D10" s="24"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9">
@@ -4937,8 +5292,8 @@
       <c r="D11" s="24"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9">
@@ -4950,8 +5305,8 @@
       <c r="D12" s="24"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9">
@@ -4963,8 +5318,8 @@
       <c r="D13" s="24"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:9">
@@ -4976,8 +5331,8 @@
       <c r="D14" s="24"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:9">
@@ -4989,8 +5344,8 @@
       <c r="D15" s="24"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:9">
@@ -5002,8 +5357,8 @@
       <c r="D16" s="24"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -5015,8 +5370,8 @@
       <c r="D17" s="24"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="26"/>
     </row>
     <row r="18" spans="1:9">
@@ -5028,8 +5383,8 @@
       <c r="D18" s="24"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:9">
@@ -5037,9 +5392,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="9"/>
       <c r="I19" s="26"/>
     </row>
@@ -5050,7 +5405,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="9"/>
       <c r="I20" s="26"/>
     </row>
@@ -5061,7 +5416,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="9"/>
       <c r="I21" s="26"/>
     </row>
@@ -5072,7 +5427,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="9"/>
       <c r="I22" s="26"/>
     </row>
@@ -5083,7 +5438,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="9"/>
       <c r="I23" s="26"/>
     </row>
@@ -5094,7 +5449,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="9"/>
       <c r="I24" s="26"/>
     </row>
@@ -6122,110 +6477,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517946</Url>
-      <Description>QAFFA7D2F2TC-2102087286-517946</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="da42b8270fd9829a6a8b9b6d410a91d7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="934d0cac02f3d216c96e26d9eebd9738" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41fed91b93125e9eb81167fcc17a074a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b37f844e38ab5d6be06af21bb96d53eb" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6344,7 +6597,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="DossierOwner" ma:index="16" nillable="true" ma:displayName="Dossier owner(s)" ma:description="Person(s) owning the dossier." ma:hidden="true" ma:internalName="DossierOwner" ma:readOnly="false" ma:showField="ImnName">
+    <xsd:element name="DossierOwner" ma:index="16" nillable="true" ma:displayName="Dossier owner(s)" ma:description="Person(s) owning the dossier." ma:format="Dropdown" ma:hidden="true" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="DossierOwner" ma:showField="ImnName">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:User">
@@ -6601,18 +6854,120 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517946</Url>
+      <Description>QAFFA7D2F2TC-2102087286-517946</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA7D879-F80C-4F95-A4FB-0E8F1E25C9B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89EF4006-08D0-4994-8AB9-07D2AB3CCC53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8AB8DA2-4765-4F48-A980-E281802CDD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AE4CB33-D7A2-40BB-95ED-A8643B4697D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="03.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="160">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -337,6 +337,201 @@
   </si>
   <si>
     <t xml:space="preserve">PEDRO HENRIQUE CARNEIRO                      </t>
+  </si>
+  <si>
+    <t>MICHELE RODRIGUES</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISLAINE BERGER                             </t>
+  </si>
+  <si>
+    <t>Apólice a renovar já utilizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIMERIA CRISTINA DE SOUZA                   </t>
+  </si>
+  <si>
+    <t> Nup CANCELAMENTO 04/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATALIA REBOUCAS DE MACEDO FREITAS ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA INES CELICO                            </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 04.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARILDES JUNIOR COHEN PINTO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSUE MARQUES DA SILVA                       </t>
+  </si>
+  <si>
+    <t>RENOV.OUTRA CIA. /RENOVACAO FORA DO PRAZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL HELVECIO SILVA DAS DORES              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO FERRAZ DE MEDEIROS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNEIA DE ALMEIDA SILVA MADEIRA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO LEITE BRANDAO                          </t>
+  </si>
+  <si>
+    <t>Devido a duplicidade de propostas VC, entre ''Proposta: 0034501269
+33 e Proposta 003450127087'', cliente optou por continuar com a pr
+oposta 003450127087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANE BRUM OLIVEIRA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS HENRIQUE SOARES DA SILVA              </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMUEL PEDRO DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIVIANE CRISTINA LOMBARDO DEL SANTO          </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t>DOIS IRMAOS CONSTRUCOES E PREMOLDADOS LTDA ME</t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO FOTO: HODOMETRO COM O MOTOR LIGADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARMISON MENDES DA SILVA                     </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONICA APARECIDA NOVAES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Painel com carro desligado </t>
+  </si>
+  <si>
+    <t>GRAO DOURADO ATACADISTA E DISTRIBUIDORA DE AL</t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALANA MECANICA LTDA ME                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: DOCUMENTO DO VEICULO. HODOMETRO. CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO TENORIO DA VITORIA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANO PRETO IMPERMEABILIZACOES LTDA ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIDNEI DE OLIVEIRA ROCHA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLUCI DA ROCHA DIAS                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO CARLOS SOARES FERREIRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERALDO MACHADO CUENCA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTAVIO ESTRELA DE CARVALHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR MASCARENHAS DE ANDRADE SOUZA          </t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+O cancelamento passa a contar a partir de 23/11/25, gerando 31 dia
+s de antecipação da renovação, a regra permite até 30 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALINE DANIELE GERMANO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ROBERTO SILVESTRE                     </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: chassi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEISIANE OLIVEIRA DO NASCIMENTO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO PINTO                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERMES AUGUSTO MELLO MARTINS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO BURATTO                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAWIDSON CARLOS CAZASSA GOMES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIDNEY DE SOUZA                              </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUZ COMERCIO DE GAS LTDA ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS G DOS SANTOS FILHO EMPREENDIMENTOS ME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAN FELIPE TOFOLI                        </t>
+  </si>
+  <si>
+    <t>29/10/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO BANDEIRA DE SOUZA CPF 52108783415 </t>
+  </si>
+  <si>
+    <t>Falta de VP</t>
+  </si>
+  <si>
+    <t>13/11/25</t>
+  </si>
+  <si>
+    <t>HASSAN PARACAT CPF 06133788909</t>
+  </si>
+  <si>
+    <t>Pedido do segurado</t>
   </si>
 </sst>
 </file>
@@ -387,7 +582,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,8 +595,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -609,12 +810,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -664,7 +907,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -769,6 +1011,52 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1153,7 +1441,7 @@
       <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <v>45964</v>
       </c>
       <c r="D2" s="18" t="s">
@@ -1168,10 +1456,10 @@
       <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="H2" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="44" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1182,10 +1470,10 @@
       <c r="B3" s="7">
         <v>45966</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="26">
         <v>45964</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>135123173</v>
       </c>
       <c r="E3" s="18">
@@ -1197,10 +1485,10 @@
       <c r="G3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1211,10 +1499,10 @@
       <c r="B4" s="7">
         <v>45955</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45964</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>135105244</v>
       </c>
       <c r="E4" s="18">
@@ -1226,10 +1514,10 @@
       <c r="G4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="44">
         <v>45955</v>
       </c>
     </row>
@@ -1240,10 +1528,10 @@
       <c r="B5" s="7">
         <v>45958</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45964</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>135133421</v>
       </c>
       <c r="E5" s="18">
@@ -1255,10 +1543,10 @@
       <c r="G5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1269,10 +1557,10 @@
       <c r="B6" s="7">
         <v>45958</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45964</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>135140502</v>
       </c>
       <c r="E6" s="18">
@@ -1284,10 +1572,10 @@
       <c r="G6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1298,10 +1586,10 @@
       <c r="B7" s="7">
         <v>45958</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45964</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>135137538</v>
       </c>
       <c r="E7" s="18">
@@ -1310,13 +1598,13 @@
       <c r="F7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1327,10 +1615,10 @@
       <c r="B8" s="7">
         <v>45958</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45964</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>135133617</v>
       </c>
       <c r="E8" s="18">
@@ -1339,13 +1627,13 @@
       <c r="F8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="H8" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1356,10 +1644,10 @@
       <c r="B9" s="7">
         <v>45958</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45964</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>135133236</v>
       </c>
       <c r="E9" s="18">
@@ -1371,10 +1659,10 @@
       <c r="G9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="49" t="s">
+      <c r="H9" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1385,10 +1673,10 @@
       <c r="B10" s="7">
         <v>45959</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45964</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>135155674</v>
       </c>
       <c r="E10" s="18">
@@ -1400,10 +1688,10 @@
       <c r="G10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1414,10 +1702,10 @@
       <c r="B11" s="7">
         <v>45959</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45964</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>135156059</v>
       </c>
       <c r="E11" s="18">
@@ -1429,10 +1717,10 @@
       <c r="G11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1443,10 +1731,10 @@
       <c r="B12" s="7">
         <v>45959</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45964</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>135155268</v>
       </c>
       <c r="E12" s="18">
@@ -1458,10 +1746,10 @@
       <c r="G12" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -1472,10 +1760,10 @@
       <c r="B13" s="7">
         <v>45959</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45964</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>135156088</v>
       </c>
       <c r="E13" s="18">
@@ -1487,10 +1775,10 @@
       <c r="G13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1501,10 +1789,10 @@
       <c r="B14" s="7">
         <v>45959</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45964</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>135162327</v>
       </c>
       <c r="E14" s="18">
@@ -1516,10 +1804,10 @@
       <c r="G14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1530,10 +1818,10 @@
       <c r="B15" s="7">
         <v>45959</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45964</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>135163700</v>
       </c>
       <c r="E15" s="18">
@@ -1545,10 +1833,10 @@
       <c r="G15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1559,10 +1847,10 @@
       <c r="B16" s="7">
         <v>45959</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45964</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>135154363</v>
       </c>
       <c r="E16" s="18">
@@ -1574,10 +1862,10 @@
       <c r="G16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1588,10 +1876,10 @@
       <c r="B17" s="7">
         <v>45959</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45964</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>135164544</v>
       </c>
       <c r="E17" s="18">
@@ -1603,10 +1891,10 @@
       <c r="G17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1617,10 +1905,10 @@
       <c r="B18" s="7">
         <v>45959</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45964</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>135159061</v>
       </c>
       <c r="E18" s="18">
@@ -1632,10 +1920,10 @@
       <c r="G18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="46" t="s">
+      <c r="H18" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1646,10 +1934,10 @@
       <c r="B19" s="7">
         <v>45959</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45964</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>135154636</v>
       </c>
       <c r="E19" s="18">
@@ -1661,10 +1949,10 @@
       <c r="G19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="44">
         <v>45959</v>
       </c>
     </row>
@@ -1675,10 +1963,10 @@
       <c r="B20" s="7">
         <v>45972</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45964</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <v>135146609</v>
       </c>
       <c r="E20" s="18">
@@ -1690,10 +1978,10 @@
       <c r="G20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="46" t="s">
+      <c r="H20" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="44">
         <v>45972</v>
       </c>
     </row>
@@ -1704,10 +1992,10 @@
       <c r="B21" s="7">
         <v>45960</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>45964</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>135174779</v>
       </c>
       <c r="E21" s="18">
@@ -1716,13 +2004,13 @@
       <c r="F21" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="54" t="s">
+      <c r="G21" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H21" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="54">
         <v>45960</v>
       </c>
     </row>
@@ -1733,25 +2021,25 @@
       <c r="B22" s="7">
         <v>45958</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>45964</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <v>135129415</v>
       </c>
       <c r="E22" s="18">
         <v>3450123336</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="53" t="s">
+      <c r="G22" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="45">
+      <c r="I22" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1762,25 +2050,25 @@
       <c r="B23" s="7">
         <v>45980</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>45964</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <v>135171249</v>
       </c>
       <c r="E23" s="18">
         <v>3450127439</v>
       </c>
-      <c r="F23" s="48" t="s">
+      <c r="F23" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="53" t="s">
+      <c r="G23" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -1791,25 +2079,25 @@
       <c r="B24" s="7">
         <v>45960</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>45964</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <v>135168476</v>
       </c>
       <c r="E24" s="18">
         <v>3450127153</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F24" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="44">
         <v>45960</v>
       </c>
     </row>
@@ -1820,25 +2108,25 @@
       <c r="B25" s="7">
         <v>45960</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>45964</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <v>135176940</v>
       </c>
       <c r="E25" s="18">
         <v>3450128000</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="53" t="s">
+      <c r="G25" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="44">
         <v>45960</v>
       </c>
     </row>
@@ -1849,25 +2137,25 @@
       <c r="B26" s="7">
         <v>45960</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>45964</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="23">
         <v>135180725</v>
       </c>
       <c r="E26" s="18">
         <v>3450128418</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="G26" s="52" t="s">
         <v>13</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="44">
         <v>45964</v>
       </c>
     </row>
@@ -1878,25 +2166,25 @@
       <c r="B27" s="7">
         <v>45961</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>45964</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <v>135193358</v>
       </c>
       <c r="E27" s="18">
         <v>3450129485</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="53" t="s">
+      <c r="G27" s="52" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -1907,25 +2195,25 @@
       <c r="B28" s="7">
         <v>45961</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>45964</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>135191401</v>
       </c>
       <c r="E28" s="18">
         <v>3450129166</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="53" t="s">
+      <c r="G28" s="52" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="45">
+      <c r="I28" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -1936,25 +2224,25 @@
       <c r="B29" s="7">
         <v>45961</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>45964</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>135200685</v>
       </c>
       <c r="E29" s="18">
         <v>3450130376</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="53" t="s">
+      <c r="G29" s="52" t="s">
         <v>32</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="45">
+      <c r="I29" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -1965,25 +2253,25 @@
       <c r="B30" s="7">
         <v>45958</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <v>45964</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>135133426</v>
       </c>
       <c r="E30" s="18">
         <v>3450123754</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="53" t="s">
+      <c r="G30" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="45">
+      <c r="I30" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -1994,25 +2282,25 @@
       <c r="B31" s="7">
         <v>45958</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>45964</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>135139336</v>
       </c>
       <c r="E31" s="18">
         <v>3450124425</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="53" t="s">
+      <c r="G31" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I31" s="45">
+      <c r="I31" s="44">
         <v>45958</v>
       </c>
     </row>
@@ -2023,25 +2311,25 @@
       <c r="B32" s="7">
         <v>45954</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="26">
         <v>45964</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <v>135110534</v>
       </c>
       <c r="E32" s="18">
         <v>3450120290</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="53" t="s">
+      <c r="G32" s="52" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="I32" s="45">
+      <c r="I32" s="44">
         <v>45954</v>
       </c>
     </row>
@@ -2052,25 +2340,25 @@
       <c r="B33" s="7">
         <v>45954</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <v>45964</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="23">
         <v>135100251</v>
       </c>
       <c r="E33" s="18">
         <v>3450121004</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="45">
+      <c r="I33" s="44">
         <v>45961</v>
       </c>
     </row>
@@ -2081,25 +2369,25 @@
       <c r="B34" s="7">
         <v>45957</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <v>45964</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>135116743</v>
       </c>
       <c r="E34" s="18">
         <v>3450122313</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="44">
         <v>45957</v>
       </c>
     </row>
@@ -2110,100 +2398,100 @@
       <c r="B35" s="7">
         <v>45957</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="26">
         <v>45964</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="23">
         <v>135111233</v>
       </c>
       <c r="E35" s="18">
         <v>3450121642</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="53" t="s">
+      <c r="G35" s="52" t="s">
         <v>39</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="45">
+      <c r="I35" s="44">
         <v>45961</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="24"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="26"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="52"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="51"/>
       <c r="G37" s="20"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="26"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="18"/>
       <c r="F38" s="12"/>
-      <c r="G38" s="23"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="26"/>
+      <c r="I38" s="25"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="24"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="18"/>
       <c r="F39" s="12"/>
-      <c r="G39" s="23"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="26"/>
+      <c r="I39" s="25"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="24"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="18"/>
       <c r="F40" s="19"/>
       <c r="G40" s="20"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="26"/>
+      <c r="I40" s="25"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="24"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="18"/>
       <c r="F41" s="19"/>
       <c r="G41" s="20"/>
       <c r="H41" s="9"/>
-      <c r="I41" s="26"/>
+      <c r="I41" s="25"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="15"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
@@ -2412,16 +2700,16 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="45">
+      <c r="A2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="44">
         <v>45964</v>
       </c>
-      <c r="C2" s="45">
+      <c r="C2" s="44">
         <v>45965</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="18">
@@ -2430,40 +2718,40 @@
       <c r="F2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="45"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="57">
         <v>45964</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="58">
         <v>45965</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="18">
         <v>3450131520</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="45"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2472,25 +2760,25 @@
       <c r="B4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>45965</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="60">
         <v>135057851</v>
       </c>
       <c r="E4" s="18">
         <v>3450117429</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="61" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="57">
         <v>45952</v>
       </c>
     </row>
@@ -2501,22 +2789,22 @@
       <c r="B5" s="7">
         <v>45959</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>45965</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="60">
         <v>135051461</v>
       </c>
       <c r="E5" s="18">
         <v>3450116714</v>
       </c>
-      <c r="F5" s="62" t="s">
+      <c r="F5" s="61" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="45" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="7">
@@ -2530,22 +2818,22 @@
       <c r="B6" s="7">
         <v>45952</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>45965</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="60">
         <v>135051444</v>
       </c>
       <c r="E6" s="18">
         <v>3450116703</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="61" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="46" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="7">
@@ -2559,22 +2847,22 @@
       <c r="B7" s="7">
         <v>45952</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>45965</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="60">
         <v>135043044</v>
       </c>
       <c r="E7" s="18">
         <v>3450115746</v>
       </c>
-      <c r="F7" s="62" t="s">
+      <c r="F7" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="47" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="7">
@@ -2588,22 +2876,22 @@
       <c r="B8" s="7">
         <v>45952</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>45965</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="60">
         <v>135044605</v>
       </c>
       <c r="E8" s="18">
         <v>3450115856</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="61" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="49" t="s">
+      <c r="H8" s="48" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="7">
@@ -2617,22 +2905,22 @@
       <c r="B9" s="7">
         <v>45952</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>45965</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="60">
         <v>135048417</v>
       </c>
       <c r="E9" s="18">
         <v>3450116197</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="F9" s="61" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="7">
@@ -2646,22 +2934,22 @@
       <c r="B10" s="7">
         <v>45952</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>45965</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="60">
         <v>135049114</v>
       </c>
       <c r="E10" s="18">
         <v>3450116351</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F10" s="61" t="s">
         <v>86</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="7">
@@ -2675,22 +2963,22 @@
       <c r="B11" s="7">
         <v>45952</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>45965</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="60">
         <v>135049373</v>
       </c>
       <c r="E11" s="18">
         <v>3450116373</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="61" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="7">
@@ -2704,22 +2992,22 @@
       <c r="B12" s="7">
         <v>45952</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>45965</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="60">
         <v>135051429</v>
       </c>
       <c r="E12" s="18">
         <v>3450116681</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="61" t="s">
         <v>88</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="7">
@@ -2733,22 +3021,22 @@
       <c r="B13" s="7">
         <v>45952</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>45965</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="60">
         <v>135051570</v>
       </c>
       <c r="E13" s="18">
         <v>3450116725</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="61" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="7">
@@ -2762,22 +3050,22 @@
       <c r="B14" s="7">
         <v>45952</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>45965</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="60">
         <v>135056953</v>
       </c>
       <c r="E14" s="18">
         <v>3450117253</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="61" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="7">
@@ -2791,22 +3079,22 @@
       <c r="B15" s="7">
         <v>45952</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>45965</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="60">
         <v>135057252</v>
       </c>
       <c r="E15" s="18">
         <v>3450117352</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="61" t="s">
         <v>91</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="7">
@@ -2820,22 +3108,22 @@
       <c r="B16" s="7">
         <v>45952</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>45965</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="60">
         <v>135057776</v>
       </c>
       <c r="E16" s="18">
         <v>3450117418</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="61" t="s">
         <v>92</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I16" s="7">
@@ -2849,22 +3137,22 @@
       <c r="B17" s="7">
         <v>45952</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>45965</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="60">
         <v>135059630</v>
       </c>
       <c r="E17" s="18">
         <v>3450117649</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="61" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="7">
@@ -2878,22 +3166,22 @@
       <c r="B18" s="7">
         <v>45952</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>45965</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="60">
         <v>135059784</v>
       </c>
       <c r="E18" s="18">
         <v>3450117682</v>
       </c>
-      <c r="F18" s="62" t="s">
+      <c r="F18" s="61" t="s">
         <v>94</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="46" t="s">
+      <c r="H18" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="7">
@@ -2907,22 +3195,22 @@
       <c r="B19" s="7">
         <v>45952</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>45965</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="60">
         <v>135061235</v>
       </c>
       <c r="E19" s="18">
         <v>3450117759</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="61" t="s">
         <v>95</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="7">
@@ -2936,22 +3224,22 @@
       <c r="B20" s="7">
         <v>45952</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>45965</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="60">
         <v>135055840</v>
       </c>
       <c r="E20" s="18">
         <v>3450117110</v>
       </c>
-      <c r="F20" s="62" t="s">
+      <c r="F20" s="61" t="s">
         <v>96</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="46" t="s">
+      <c r="H20" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="7">
@@ -2961,156 +3249,156 @@
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="18"/>
       <c r="F21" s="12"/>
       <c r="G21" s="20"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="18"/>
       <c r="F22" s="12"/>
       <c r="G22" s="20"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="23"/>
       <c r="E23" s="18"/>
       <c r="F23" s="12"/>
       <c r="G23" s="20"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="18"/>
       <c r="F24" s="12"/>
       <c r="G24" s="20"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="24"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="18"/>
       <c r="F25" s="12"/>
       <c r="G25" s="20"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="24"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="18"/>
       <c r="F26" s="12"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="26"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="18"/>
       <c r="F27" s="12"/>
       <c r="G27" s="20"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="24"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
       <c r="G28" s="20"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12"/>
       <c r="G29" s="20"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
       <c r="G30" s="20"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="18"/>
       <c r="F31" s="12"/>
       <c r="G31" s="20"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="18"/>
       <c r="F32" s="12"/>
       <c r="G32" s="20"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="18"/>
       <c r="F33" s="12"/>
       <c r="G33" s="20"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="15"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -3121,7 +3409,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -3132,7 +3420,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -3363,7 +3651,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
@@ -3373,7 +3661,7 @@
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="26" customWidth="1"/>
+    <col min="9" max="9" width="21" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3401,477 +3689,1184 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
+      <c r="A2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="26">
+        <v>45965</v>
+      </c>
+      <c r="C2" s="44">
+        <v>45966</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="65">
+        <v>3450134402</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="26">
+        <v>45953</v>
+      </c>
+      <c r="C3" s="44">
+        <v>45966</v>
+      </c>
+      <c r="D3" s="75">
+        <v>135076900</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450118848</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="44">
+        <v>45966</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="26">
+        <v>45954</v>
+      </c>
+      <c r="C4" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D4" s="18">
+        <v>135099564</v>
+      </c>
+      <c r="E4" s="71">
+        <v>3450120905</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="54">
+        <v>45965</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="A5" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="76">
+        <v>45957</v>
+      </c>
+      <c r="C5" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D5" s="18">
+        <v>135128663</v>
+      </c>
+      <c r="E5" s="72">
+        <v>3450122775</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="44">
+        <v>45957</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="77">
+        <v>45957</v>
+      </c>
+      <c r="C6" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D6" s="18">
+        <v>135128447</v>
+      </c>
+      <c r="E6" s="71">
+        <v>3450122797</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" s="44">
+        <v>45965</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C7" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D7" s="18">
+        <v>135136881</v>
+      </c>
+      <c r="E7" s="71">
+        <v>3450124172</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C8" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D8" s="18">
+        <v>135139953</v>
+      </c>
+      <c r="E8" s="71">
+        <v>3450124513</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="44">
+        <v>45966</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C9" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D9" s="18">
+        <v>135141304</v>
+      </c>
+      <c r="E9" s="71">
+        <v>3450124645</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C10" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D10" s="18">
+        <v>135135779</v>
+      </c>
+      <c r="E10" s="71">
+        <v>3450124106</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C11" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D11" s="18">
+        <v>135143557</v>
+      </c>
+      <c r="E11" s="71">
+        <v>3450124910</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="77">
+        <v>45959</v>
+      </c>
+      <c r="C12" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D12" s="18">
+        <v>135163415</v>
+      </c>
+      <c r="E12" s="71">
+        <v>3450126933</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="44">
+        <v>45965</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C13" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D13" s="18">
+        <v>135144707</v>
+      </c>
+      <c r="E13" s="71">
+        <v>3450125020</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="77">
+        <v>45960</v>
+      </c>
+      <c r="C14" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D14" s="18">
+        <v>135167327</v>
+      </c>
+      <c r="E14" s="71">
+        <v>3450127076</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="44">
+        <v>45960</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="77">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D15" s="18">
+        <v>135142892</v>
+      </c>
+      <c r="E15" s="71">
+        <v>3450124799</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="44">
+        <v>45958</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
+      <c r="B16" s="77">
+        <v>45960</v>
+      </c>
+      <c r="C16" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D16" s="18">
+        <v>135169853</v>
+      </c>
+      <c r="E16" s="71">
+        <v>3450127263</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="44">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="77">
+        <v>45960</v>
+      </c>
+      <c r="C17" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D17" s="18">
+        <v>135175287</v>
+      </c>
+      <c r="E17" s="71">
+        <v>3450127945</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="44">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="77">
+        <v>45961</v>
+      </c>
+      <c r="C18" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D18" s="18">
+        <v>135196667</v>
+      </c>
+      <c r="E18" s="71">
+        <v>3450129793</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="I18" s="44">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="77">
+        <v>45961</v>
+      </c>
+      <c r="C19" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D19" s="18">
+        <v>135198665</v>
+      </c>
+      <c r="E19" s="71">
+        <v>3450130134</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="44">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="77">
+        <v>45961</v>
+      </c>
+      <c r="C20" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D20" s="18">
+        <v>135189146</v>
+      </c>
+      <c r="E20" s="71">
+        <v>3450128902</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="44">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="77">
+        <v>45961</v>
+      </c>
+      <c r="C21" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D21" s="18">
+        <v>135196535</v>
+      </c>
+      <c r="E21" s="71">
+        <v>3450129760</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="44">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="77">
+        <v>45959</v>
+      </c>
+      <c r="C22" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D22" s="18">
+        <v>135162952</v>
+      </c>
+      <c r="E22" s="71">
+        <v>3450126856</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="77">
+        <v>45964</v>
+      </c>
+      <c r="C23" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D23" s="18">
+        <v>135217292</v>
+      </c>
+      <c r="E23" s="71">
+        <v>3450132257</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="44">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="77">
+        <v>45978</v>
+      </c>
+      <c r="C24" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D24" s="18">
+        <v>135221235</v>
+      </c>
+      <c r="E24" s="71">
+        <v>3450132708</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="77">
+        <v>45969</v>
+      </c>
+      <c r="C25" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D25" s="18">
+        <v>135213060</v>
+      </c>
+      <c r="E25" s="71">
+        <v>3450131685</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="44">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="77">
+        <v>45969</v>
+      </c>
+      <c r="C26" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D26" s="18">
+        <v>135211114</v>
+      </c>
+      <c r="E26" s="71">
+        <v>3450131289</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="77">
+        <v>45954</v>
+      </c>
+      <c r="C27" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D27" s="18">
+        <v>135099857</v>
+      </c>
+      <c r="E27" s="71">
+        <v>3450120938</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="77">
+        <v>45953</v>
+      </c>
+      <c r="C28" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D28" s="18">
+        <v>135083116</v>
+      </c>
+      <c r="E28" s="71">
+        <v>3450118056</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="77">
+        <v>45972</v>
+      </c>
+      <c r="C29" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D29" s="18">
+        <v>135148512</v>
+      </c>
+      <c r="E29" s="71">
+        <v>3450125151</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="I29" s="44">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="77">
+        <v>45953</v>
+      </c>
+      <c r="C30" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D30" s="18">
+        <v>135069472</v>
+      </c>
+      <c r="E30" s="71">
+        <v>3450118254</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="78" t="s">
+        <v>139</v>
+      </c>
+      <c r="I30" s="44">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="77">
+        <v>45960</v>
+      </c>
+      <c r="C31" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D31" s="18">
+        <v>135177588</v>
+      </c>
+      <c r="E31" s="71">
+        <v>3450128033</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="44">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C32" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D32" s="18">
+        <v>135198288</v>
+      </c>
+      <c r="E32" s="71">
+        <v>3450130046</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="44">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C33" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D33" s="18">
+        <v>135127470</v>
+      </c>
+      <c r="E33" s="71">
+        <v>3450123226</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="44">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C34" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D34" s="18">
+        <v>135127916</v>
+      </c>
+      <c r="E34" s="71">
+        <v>3450123248</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="44">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C35" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D35" s="18">
+        <v>135128652</v>
+      </c>
+      <c r="E35" s="73">
+        <v>3450123260</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="44">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45957</v>
+      </c>
+      <c r="C36" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D36" s="18">
+        <v>135130128</v>
+      </c>
+      <c r="E36" s="74">
+        <v>3450122016</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="44">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C37" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D37" s="18">
+        <v>135134019</v>
+      </c>
+      <c r="E37" s="74">
+        <v>3450123897</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="44">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C38" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D38" s="18">
+        <v>135134249</v>
+      </c>
+      <c r="E38" s="74">
+        <v>3450123930</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="I38" s="44">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C39" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D39" s="18">
+        <v>135138811</v>
+      </c>
+      <c r="E39" s="74">
+        <v>3450124360</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="44">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C40" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D40" s="18">
+        <v>135142007</v>
+      </c>
+      <c r="E40" s="74">
+        <v>3450124690</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="44">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C41" s="70">
+        <v>45966</v>
+      </c>
+      <c r="D41" s="18">
+        <v>135144041</v>
+      </c>
+      <c r="E41" s="74">
+        <v>3450124997</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="44">
+        <v>45958</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A41" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B20" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B20" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3926,27 +4921,55 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="B2" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="44">
+        <v>45819</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450126900</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="B3" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="44">
+        <v>45819</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450130871</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3954,12 +4977,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="28"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="8"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="29"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -3967,12 +4990,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="8"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="29"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -3980,12 +5003,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="8"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="29"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -3993,12 +5016,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="28"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="8"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="29"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -4006,12 +5029,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="28"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="8"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="29"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="26"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -4019,12 +5042,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="28"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="8"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="26"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -4032,12 +5055,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="28"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="8"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -4045,12 +5068,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="29"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -4058,12 +5081,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="28"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="8"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="29"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -4071,12 +5094,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="28"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="8"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -4084,12 +5107,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="29"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -4097,23 +5120,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="28"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="8"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="29"/>
+      <c r="G15" s="28"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="28"/>
+      <c r="D16" s="27"/>
       <c r="E16" s="8"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="29"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4124,7 +5147,7 @@
       <c r="F17" s="12"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4135,7 +5158,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4146,7 +5169,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4157,7 +5180,7 @@
       <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4515,13 +5538,14 @@
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{5A2669B6-989B-49D6-BBDC-D101598AEC55}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4576,63 +5600,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="12"/>
       <c r="G2" s="20"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="36"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="12"/>
       <c r="G4" s="20"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12"/>
       <c r="G5" s="20"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -5159,7 +6183,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5171,232 +6195,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="26"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="26"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="26"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="26"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="26"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="26"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="26"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="26"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="26"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="26"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="26"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="26"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="32"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5405,9 +6429,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="32"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5416,9 +6440,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="32"/>
+      <c r="G21" s="31"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -5427,9 +6451,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="32"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5438,9 +6462,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="32"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5449,9 +6473,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5462,7 +6486,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5473,7 +6497,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="26"/>
+      <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5484,7 +6508,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -5495,7 +6519,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -5506,7 +6530,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -5517,7 +6541,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="26"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -5528,7 +6552,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -5539,7 +6563,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="26"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -5550,7 +6574,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="26"/>
+      <c r="I33" s="25"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -5561,7 +6585,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -5572,7 +6596,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35" s="25"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6477,6 +7501,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41fed91b93125e9eb81167fcc17a074a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b37f844e38ab5d6be06af21bb96d53eb" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6854,7 +7937,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
@@ -6897,77 +7980,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA7D879-F80C-4F95-A4FB-0E8F1E25C9B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8C0D9C2-4E68-45AE-8716-787772E9A414}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AE4CB33-D7A2-40BB-95ED-A8643B4697D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A0A34D-06C1-4C60-B9CE-7DC693712C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="03.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="220">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -516,29 +516,212 @@
     <t xml:space="preserve">WILLIAN FELIPE TOFOLI                        </t>
   </si>
   <si>
-    <t>29/10/25</t>
-  </si>
-  <si>
     <t xml:space="preserve">CARLOS EDUARDO BANDEIRA DE SOUZA CPF 52108783415 </t>
   </si>
   <si>
     <t>Falta de VP</t>
   </si>
   <si>
-    <t>13/11/25</t>
-  </si>
-  <si>
     <t>HASSAN PARACAT CPF 06133788909</t>
   </si>
   <si>
     <t>Pedido do segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESORT FAROL DAS DUNAS LTDA EPP              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS SILVA DE SOUZA                        </t>
+  </si>
+  <si>
+    <t>Falta de vistoria </t>
+  </si>
+  <si>
+    <t>NOVA SUPREMA RIO COM DE PRODUTOS DE LIMPEZA E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATANAEL ALMEIDA CAMPOS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO FERREIRA                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ GUILHERME BENTES MARTINS JUNIOR         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALTEVI MORAIS DA SILVA                      </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPERATRIZ AGRO NEGOCIOS LTDA ME             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISETE DOS SANTOS CARLOS                    </t>
+  </si>
+  <si>
+    <t>DIVINA ARTE GALERIA COMERCIO DE ARTESANATOS L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL JOSE SPADA BONFIM                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANIR FREITAS CAVALCANTE                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELENIR CUCHI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFFERSON JOSE RODRIGUES QUEIROZ             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN BATISTA DE MOURA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO HENRIQUE MEDEIROS DE BRITO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILAINE SIMAO VALERIO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALDO DE ABREU ALVES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ CARLOS RODRIGUES DA SILVA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO BANDEIRA DE SOUZA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONATAS DIAS DE ALMEIDA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO LEITE CASCIANO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO DINIZ DE ALMEIDA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBSON DA SILVA CORREA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FRUSTRADO repique: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t>TEMPERTECH COMERCIO DE VIDROS E ALUMINIOS LTD</t>
+  </si>
+  <si>
+    <t>FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do mot, T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILMAR BATISTA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA APARECIDA DOS ANJOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATARINA LUCIA GOMES DE FARIA DIAS           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANO RAMOS DA CONCEICAO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIKA MARIANE SOARES DE OLIVEIRA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO IVO PORTO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIULIO MENDES PIETROPAOLO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATO APARECIDO BORGES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS PAULO REBELATTO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO ARTHUR LIMA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FERNANDO DE CARVALHO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARY FERREIRA COELHO JUNIOR                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAI PERRI DE MORAES                          </t>
+  </si>
+  <si>
+    <t>CLINICA SETTI ODONTOLOGIA E ESTETICA IMPORT L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO CRISTIANO DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCADO PORTO REAL LTDA EPP                  </t>
+  </si>
+  <si>
+    <t>Divergência de bônus.     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMARA MOREIRA DE MACEDO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICKSON SOUSA BERGUE                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDER MATHIAS TORREZANI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divergência de bônus.     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO GOMES DE BORBA                         </t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, de INCÊNDIO E ROUBO para COMPREENSIVA, ocorre a redução de 1 cl
+asse de bônus, assim sendo o correto bônus 0.&lt;br&gt;Com a correção fi
+cou 10x R$ 507,65. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPEDITO BARROSO DE ALENCAR FILHO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO ROCHA RODRIGUES DA SILVA             </t>
+  </si>
+  <si>
+    <t>SEXY FLOWER LOVE COMERCIO DE ARTIGOS EROTICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO DA SILVA SANTOS               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETELVINA MARIA DE FREITAS FERREIRA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOVANI CRISTIAN DA SILVA AMARAL             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIANE FRAGA DE ARAUJO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILMAR MAURICIO PESCADOR AGUDELO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAUL QUEIROZ LUCIO DOS SANTOS                </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,6 +764,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -602,7 +791,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -852,12 +1041,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -924,9 +1155,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1056,7 +1284,44 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1456,10 +1721,10 @@
       <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1485,10 +1750,10 @@
       <c r="G3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1514,10 +1779,10 @@
       <c r="G4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>45955</v>
       </c>
     </row>
@@ -1543,10 +1808,10 @@
       <c r="G5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -1572,10 +1837,10 @@
       <c r="G6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -1601,10 +1866,10 @@
       <c r="G7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -1630,10 +1895,10 @@
       <c r="G8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -1659,10 +1924,10 @@
       <c r="G9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -1688,10 +1953,10 @@
       <c r="G10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1717,10 +1982,10 @@
       <c r="G11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1746,10 +2011,10 @@
       <c r="G12" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -1775,10 +2040,10 @@
       <c r="G13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1804,10 +2069,10 @@
       <c r="G14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1833,10 +2098,10 @@
       <c r="G15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1862,10 +2127,10 @@
       <c r="G16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1891,10 +2156,10 @@
       <c r="G17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1920,10 +2185,10 @@
       <c r="G18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1949,10 +2214,10 @@
       <c r="G19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -1978,10 +2243,10 @@
       <c r="G20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>45972</v>
       </c>
     </row>
@@ -2004,13 +2269,13 @@
       <c r="F21" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="53" t="s">
+      <c r="G21" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="54">
+      <c r="I21" s="53">
         <v>45960</v>
       </c>
     </row>
@@ -2030,16 +2295,16 @@
       <c r="E22" s="18">
         <v>3450123336</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="52" t="s">
+      <c r="G22" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -2059,16 +2324,16 @@
       <c r="E23" s="18">
         <v>3450127439</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="52" t="s">
+      <c r="G23" s="51" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2088,16 +2353,16 @@
       <c r="E24" s="18">
         <v>3450127153</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="52" t="s">
+      <c r="G24" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -2117,16 +2382,16 @@
       <c r="E25" s="18">
         <v>3450128000</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="52" t="s">
+      <c r="G25" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -2146,16 +2411,16 @@
       <c r="E26" s="18">
         <v>3450128418</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="52" t="s">
+      <c r="G26" s="51" t="s">
         <v>13</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>45964</v>
       </c>
     </row>
@@ -2175,16 +2440,16 @@
       <c r="E27" s="18">
         <v>3450129485</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="52" t="s">
+      <c r="G27" s="51" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2204,16 +2469,16 @@
       <c r="E28" s="18">
         <v>3450129166</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="51" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2233,16 +2498,16 @@
       <c r="E29" s="18">
         <v>3450130376</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="52" t="s">
+      <c r="G29" s="51" t="s">
         <v>32</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2262,16 +2527,16 @@
       <c r="E30" s="18">
         <v>3450123754</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="52" t="s">
+      <c r="G30" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -2291,16 +2556,16 @@
       <c r="E31" s="18">
         <v>3450124425</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="52" t="s">
+      <c r="G31" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -2320,16 +2585,16 @@
       <c r="E32" s="18">
         <v>3450120290</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="52" t="s">
+      <c r="G32" s="51" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>45954</v>
       </c>
     </row>
@@ -2349,16 +2614,16 @@
       <c r="E33" s="18">
         <v>3450121004</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="G33" s="52" t="s">
+      <c r="G33" s="51" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2378,16 +2643,16 @@
       <c r="E34" s="18">
         <v>3450122313</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="52" t="s">
+      <c r="G34" s="51" t="s">
         <v>39</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>45957</v>
       </c>
     </row>
@@ -2407,16 +2672,16 @@
       <c r="E35" s="18">
         <v>3450121642</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="52" t="s">
+      <c r="G35" s="51" t="s">
         <v>39</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -2427,17 +2692,17 @@
       <c r="D36" s="23"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="45"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="51"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="50"/>
       <c r="G37" s="20"/>
       <c r="H37" s="9"/>
       <c r="I37" s="25"/>
@@ -2700,13 +2965,13 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="44">
+      <c r="A2" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="43">
         <v>45964</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="43">
         <v>45965</v>
       </c>
       <c r="D2" s="23" t="s">
@@ -2718,22 +2983,22 @@
       <c r="F2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="56">
         <v>45964</v>
       </c>
-      <c r="C3" s="58">
+      <c r="C3" s="57">
         <v>45965</v>
       </c>
       <c r="D3" s="23" t="s">
@@ -2742,16 +3007,16 @@
       <c r="E3" s="18">
         <v>3450131520</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2763,22 +3028,22 @@
       <c r="C4" s="26">
         <v>45965</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="59">
         <v>135057851</v>
       </c>
       <c r="E4" s="18">
         <v>3450117429</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="60" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="57">
+      <c r="I4" s="56">
         <v>45952</v>
       </c>
     </row>
@@ -2792,19 +3057,19 @@
       <c r="C5" s="26">
         <v>45965</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <v>135051461</v>
       </c>
       <c r="E5" s="18">
         <v>3450116714</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="60" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="7">
@@ -2821,19 +3086,19 @@
       <c r="C6" s="26">
         <v>45965</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="59">
         <v>135051444</v>
       </c>
       <c r="E6" s="18">
         <v>3450116703</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="F6" s="60" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="45" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="7">
@@ -2850,19 +3115,19 @@
       <c r="C7" s="26">
         <v>45965</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="59">
         <v>135043044</v>
       </c>
       <c r="E7" s="18">
         <v>3450115746</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="60" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="7">
@@ -2879,19 +3144,19 @@
       <c r="C8" s="26">
         <v>45965</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="59">
         <v>135044605</v>
       </c>
       <c r="E8" s="18">
         <v>3450115856</v>
       </c>
-      <c r="F8" s="61" t="s">
+      <c r="F8" s="60" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="H8" s="47" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="7">
@@ -2908,19 +3173,19 @@
       <c r="C9" s="26">
         <v>45965</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="59">
         <v>135048417</v>
       </c>
       <c r="E9" s="18">
         <v>3450116197</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="60" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="7">
@@ -2937,19 +3202,19 @@
       <c r="C10" s="26">
         <v>45965</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="59">
         <v>135049114</v>
       </c>
       <c r="E10" s="18">
         <v>3450116351</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="60" t="s">
         <v>86</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="7">
@@ -2966,19 +3231,19 @@
       <c r="C11" s="26">
         <v>45965</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="59">
         <v>135049373</v>
       </c>
       <c r="E11" s="18">
         <v>3450116373</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="60" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="7">
@@ -2995,19 +3260,19 @@
       <c r="C12" s="26">
         <v>45965</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="59">
         <v>135051429</v>
       </c>
       <c r="E12" s="18">
         <v>3450116681</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="60" t="s">
         <v>88</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="7">
@@ -3024,19 +3289,19 @@
       <c r="C13" s="26">
         <v>45965</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="59">
         <v>135051570</v>
       </c>
       <c r="E13" s="18">
         <v>3450116725</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="60" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="7">
@@ -3053,19 +3318,19 @@
       <c r="C14" s="26">
         <v>45965</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="59">
         <v>135056953</v>
       </c>
       <c r="E14" s="18">
         <v>3450117253</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F14" s="60" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="7">
@@ -3082,19 +3347,19 @@
       <c r="C15" s="26">
         <v>45965</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="59">
         <v>135057252</v>
       </c>
       <c r="E15" s="18">
         <v>3450117352</v>
       </c>
-      <c r="F15" s="61" t="s">
+      <c r="F15" s="60" t="s">
         <v>91</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="7">
@@ -3111,19 +3376,19 @@
       <c r="C16" s="26">
         <v>45965</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="59">
         <v>135057776</v>
       </c>
       <c r="E16" s="18">
         <v>3450117418</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="60" t="s">
         <v>92</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I16" s="7">
@@ -3140,19 +3405,19 @@
       <c r="C17" s="26">
         <v>45965</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="59">
         <v>135059630</v>
       </c>
       <c r="E17" s="18">
         <v>3450117649</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="60" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="7">
@@ -3169,19 +3434,19 @@
       <c r="C18" s="26">
         <v>45965</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="59">
         <v>135059784</v>
       </c>
       <c r="E18" s="18">
         <v>3450117682</v>
       </c>
-      <c r="F18" s="61" t="s">
+      <c r="F18" s="60" t="s">
         <v>94</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="7">
@@ -3198,19 +3463,19 @@
       <c r="C19" s="26">
         <v>45965</v>
       </c>
-      <c r="D19" s="60">
+      <c r="D19" s="59">
         <v>135061235</v>
       </c>
       <c r="E19" s="18">
         <v>3450117759</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="60" t="s">
         <v>95</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="7">
@@ -3227,19 +3492,19 @@
       <c r="C20" s="26">
         <v>45965</v>
       </c>
-      <c r="D20" s="60">
+      <c r="D20" s="59">
         <v>135055840</v>
       </c>
       <c r="E20" s="18">
         <v>3450117110</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="60" t="s">
         <v>96</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="7">
@@ -3309,7 +3574,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="12"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="29"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="25"/>
     </row>
     <row r="27" spans="1:9">
@@ -3689,36 +3954,36 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="51" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="26">
         <v>45965</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="43">
         <v>45966</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="64">
         <v>3450134402</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="51" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3729,83 +3994,83 @@
       <c r="B3" s="26">
         <v>45953</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="43">
         <v>45966</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="74">
         <v>135076900</v>
       </c>
       <c r="E3" s="18">
         <v>3450118848</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="43">
         <v>45966</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="26">
         <v>45954</v>
       </c>
-      <c r="C4" s="70">
+      <c r="C4" s="69">
         <v>45966</v>
       </c>
       <c r="D4" s="18">
         <v>135099564</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="70">
         <v>3450120905</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="67" t="s">
         <v>39</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="53">
         <v>45965</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="76">
+      <c r="A5" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="75">
         <v>45957</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="69">
         <v>45966</v>
       </c>
       <c r="D5" s="18">
         <v>135128663</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="71">
         <v>3450122775</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>45957</v>
       </c>
     </row>
@@ -3813,16 +4078,16 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="76">
         <v>45957</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="69">
         <v>45966</v>
       </c>
       <c r="D6" s="18">
         <v>135128447</v>
       </c>
-      <c r="E6" s="71">
+      <c r="E6" s="70">
         <v>3450122797</v>
       </c>
       <c r="F6" s="13" t="s">
@@ -3831,10 +4096,10 @@
       <c r="G6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -3842,16 +4107,16 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="76">
         <v>45958</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="69">
         <v>45966</v>
       </c>
       <c r="D7" s="18">
         <v>135136881</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="70">
         <v>3450124172</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -3860,10 +4125,10 @@
       <c r="G7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -3871,16 +4136,16 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="77">
+      <c r="B8" s="76">
         <v>45958</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="69">
         <v>45966</v>
       </c>
       <c r="D8" s="18">
         <v>135139953</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="70">
         <v>3450124513</v>
       </c>
       <c r="F8" s="13" t="s">
@@ -3889,10 +4154,10 @@
       <c r="G8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>45966</v>
       </c>
     </row>
@@ -3900,16 +4165,16 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="76">
         <v>45958</v>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="69">
         <v>45966</v>
       </c>
       <c r="D9" s="18">
         <v>135141304</v>
       </c>
-      <c r="E9" s="71">
+      <c r="E9" s="70">
         <v>3450124645</v>
       </c>
       <c r="F9" s="13" t="s">
@@ -3918,10 +4183,10 @@
       <c r="G9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -3929,16 +4194,16 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="77">
+      <c r="B10" s="76">
         <v>45958</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="69">
         <v>45966</v>
       </c>
       <c r="D10" s="18">
         <v>135135779</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="70">
         <v>3450124106</v>
       </c>
       <c r="F10" s="13" t="s">
@@ -3947,10 +4212,10 @@
       <c r="G10" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -3958,16 +4223,16 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="77">
+      <c r="B11" s="76">
         <v>45958</v>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="69">
         <v>45966</v>
       </c>
       <c r="D11" s="18">
         <v>135143557</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="70">
         <v>3450124910</v>
       </c>
       <c r="F11" s="13" t="s">
@@ -3976,10 +4241,10 @@
       <c r="G11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -3987,16 +4252,16 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="76">
         <v>45959</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="69">
         <v>45966</v>
       </c>
       <c r="D12" s="18">
         <v>135163415</v>
       </c>
-      <c r="E12" s="71">
+      <c r="E12" s="70">
         <v>3450126933</v>
       </c>
       <c r="F12" s="13" t="s">
@@ -4005,10 +4270,10 @@
       <c r="G12" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="78" t="s">
+      <c r="H12" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4016,16 +4281,16 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="76">
         <v>45958</v>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="69">
         <v>45966</v>
       </c>
       <c r="D13" s="18">
         <v>135144707</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="70">
         <v>3450125020</v>
       </c>
       <c r="F13" s="13" t="s">
@@ -4034,10 +4299,10 @@
       <c r="G13" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="78" t="s">
+      <c r="H13" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4045,16 +4310,16 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="77">
+      <c r="B14" s="76">
         <v>45960</v>
       </c>
-      <c r="C14" s="70">
+      <c r="C14" s="69">
         <v>45966</v>
       </c>
       <c r="D14" s="18">
         <v>135167327</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="70">
         <v>3450127076</v>
       </c>
       <c r="F14" s="13" t="s">
@@ -4063,10 +4328,10 @@
       <c r="G14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -4074,16 +4339,16 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="77">
+      <c r="B15" s="76">
         <v>45958</v>
       </c>
-      <c r="C15" s="70">
+      <c r="C15" s="69">
         <v>45966</v>
       </c>
       <c r="D15" s="18">
         <v>135142892</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="70">
         <v>3450124799</v>
       </c>
       <c r="F15" s="13" t="s">
@@ -4092,10 +4357,10 @@
       <c r="G15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4103,16 +4368,16 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="77">
+      <c r="B16" s="76">
         <v>45960</v>
       </c>
-      <c r="C16" s="70">
+      <c r="C16" s="69">
         <v>45966</v>
       </c>
       <c r="D16" s="18">
         <v>135169853</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="70">
         <v>3450127263</v>
       </c>
       <c r="F16" s="13" t="s">
@@ -4121,10 +4386,10 @@
       <c r="G16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -4132,16 +4397,16 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="77">
+      <c r="B17" s="76">
         <v>45960</v>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="69">
         <v>45966</v>
       </c>
       <c r="D17" s="18">
         <v>135175287</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="70">
         <v>3450127945</v>
       </c>
       <c r="F17" s="13" t="s">
@@ -4150,10 +4415,10 @@
       <c r="G17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -4161,16 +4426,16 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="77">
+      <c r="B18" s="76">
         <v>45961</v>
       </c>
-      <c r="C18" s="70">
+      <c r="C18" s="69">
         <v>45966</v>
       </c>
       <c r="D18" s="18">
         <v>135196667</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="70">
         <v>3450129793</v>
       </c>
       <c r="F18" s="13" t="s">
@@ -4179,10 +4444,10 @@
       <c r="G18" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -4190,16 +4455,16 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="77">
+      <c r="B19" s="76">
         <v>45961</v>
       </c>
-      <c r="C19" s="70">
+      <c r="C19" s="69">
         <v>45966</v>
       </c>
       <c r="D19" s="18">
         <v>135198665</v>
       </c>
-      <c r="E19" s="71">
+      <c r="E19" s="70">
         <v>3450130134</v>
       </c>
       <c r="F19" s="13" t="s">
@@ -4208,10 +4473,10 @@
       <c r="G19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -4219,16 +4484,16 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="77">
+      <c r="B20" s="76">
         <v>45961</v>
       </c>
-      <c r="C20" s="70">
+      <c r="C20" s="69">
         <v>45966</v>
       </c>
       <c r="D20" s="18">
         <v>135189146</v>
       </c>
-      <c r="E20" s="71">
+      <c r="E20" s="70">
         <v>3450128902</v>
       </c>
       <c r="F20" s="13" t="s">
@@ -4237,10 +4502,10 @@
       <c r="G20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -4248,16 +4513,16 @@
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="77">
+      <c r="B21" s="76">
         <v>45961</v>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="69">
         <v>45966</v>
       </c>
       <c r="D21" s="18">
         <v>135196535</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="70">
         <v>3450129760</v>
       </c>
       <c r="F21" s="13" t="s">
@@ -4266,10 +4531,10 @@
       <c r="G21" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -4277,16 +4542,16 @@
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="77">
+      <c r="B22" s="76">
         <v>45959</v>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="69">
         <v>45966</v>
       </c>
       <c r="D22" s="18">
         <v>135162952</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E22" s="70">
         <v>3450126856</v>
       </c>
       <c r="F22" s="13" t="s">
@@ -4295,10 +4560,10 @@
       <c r="G22" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4306,16 +4571,16 @@
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="77">
+      <c r="B23" s="76">
         <v>45964</v>
       </c>
-      <c r="C23" s="70">
+      <c r="C23" s="69">
         <v>45966</v>
       </c>
       <c r="D23" s="18">
         <v>135217292</v>
       </c>
-      <c r="E23" s="71">
+      <c r="E23" s="70">
         <v>3450132257</v>
       </c>
       <c r="F23" s="13" t="s">
@@ -4324,10 +4589,10 @@
       <c r="G23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>45964</v>
       </c>
     </row>
@@ -4335,16 +4600,16 @@
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="77">
+      <c r="B24" s="76">
         <v>45978</v>
       </c>
-      <c r="C24" s="70">
+      <c r="C24" s="69">
         <v>45966</v>
       </c>
       <c r="D24" s="18">
         <v>135221235</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E24" s="70">
         <v>3450132708</v>
       </c>
       <c r="F24" s="13" t="s">
@@ -4353,10 +4618,10 @@
       <c r="G24" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4364,16 +4629,16 @@
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="77">
+      <c r="B25" s="76">
         <v>45969</v>
       </c>
-      <c r="C25" s="70">
+      <c r="C25" s="69">
         <v>45966</v>
       </c>
       <c r="D25" s="18">
         <v>135213060</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="70">
         <v>3450131685</v>
       </c>
       <c r="F25" s="13" t="s">
@@ -4382,10 +4647,10 @@
       <c r="G25" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>45969</v>
       </c>
     </row>
@@ -4393,16 +4658,16 @@
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="77">
+      <c r="B26" s="76">
         <v>45969</v>
       </c>
-      <c r="C26" s="70">
+      <c r="C26" s="69">
         <v>45966</v>
       </c>
       <c r="D26" s="18">
         <v>135211114</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="70">
         <v>3450131289</v>
       </c>
       <c r="F26" s="13" t="s">
@@ -4411,10 +4676,10 @@
       <c r="G26" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4422,16 +4687,16 @@
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="77">
+      <c r="B27" s="76">
         <v>45954</v>
       </c>
-      <c r="C27" s="70">
+      <c r="C27" s="69">
         <v>45966</v>
       </c>
       <c r="D27" s="18">
         <v>135099857</v>
       </c>
-      <c r="E27" s="71">
+      <c r="E27" s="70">
         <v>3450120938</v>
       </c>
       <c r="F27" s="13" t="s">
@@ -4440,10 +4705,10 @@
       <c r="G27" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4451,16 +4716,16 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="77">
+      <c r="B28" s="76">
         <v>45953</v>
       </c>
-      <c r="C28" s="70">
+      <c r="C28" s="69">
         <v>45966</v>
       </c>
       <c r="D28" s="18">
         <v>135083116</v>
       </c>
-      <c r="E28" s="71">
+      <c r="E28" s="70">
         <v>3450118056</v>
       </c>
       <c r="F28" s="13" t="s">
@@ -4469,10 +4734,10 @@
       <c r="G28" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4480,16 +4745,16 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="77">
+      <c r="B29" s="76">
         <v>45972</v>
       </c>
-      <c r="C29" s="70">
+      <c r="C29" s="69">
         <v>45966</v>
       </c>
       <c r="D29" s="18">
         <v>135148512</v>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="70">
         <v>3450125151</v>
       </c>
       <c r="F29" s="13" t="s">
@@ -4498,10 +4763,10 @@
       <c r="G29" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>45965</v>
       </c>
     </row>
@@ -4509,16 +4774,16 @@
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="77">
+      <c r="B30" s="76">
         <v>45953</v>
       </c>
-      <c r="C30" s="70">
+      <c r="C30" s="69">
         <v>45966</v>
       </c>
       <c r="D30" s="18">
         <v>135069472</v>
       </c>
-      <c r="E30" s="71">
+      <c r="E30" s="70">
         <v>3450118254</v>
       </c>
       <c r="F30" s="13" t="s">
@@ -4527,10 +4792,10 @@
       <c r="G30" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="78" t="s">
+      <c r="H30" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>45953</v>
       </c>
     </row>
@@ -4538,16 +4803,16 @@
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="77">
+      <c r="B31" s="76">
         <v>45960</v>
       </c>
-      <c r="C31" s="70">
+      <c r="C31" s="69">
         <v>45966</v>
       </c>
       <c r="D31" s="18">
         <v>135177588</v>
       </c>
-      <c r="E31" s="71">
+      <c r="E31" s="70">
         <v>3450128033</v>
       </c>
       <c r="F31" s="13" t="s">
@@ -4556,10 +4821,10 @@
       <c r="G31" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>45960</v>
       </c>
     </row>
@@ -4570,13 +4835,13 @@
       <c r="B32" s="7">
         <v>45961</v>
       </c>
-      <c r="C32" s="70">
+      <c r="C32" s="69">
         <v>45966</v>
       </c>
       <c r="D32" s="18">
         <v>135198288</v>
       </c>
-      <c r="E32" s="71">
+      <c r="E32" s="70">
         <v>3450130046</v>
       </c>
       <c r="F32" s="13" t="s">
@@ -4585,10 +4850,10 @@
       <c r="G32" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>45961</v>
       </c>
     </row>
@@ -4599,13 +4864,13 @@
       <c r="B33" s="7">
         <v>45958</v>
       </c>
-      <c r="C33" s="70">
+      <c r="C33" s="69">
         <v>45966</v>
       </c>
       <c r="D33" s="18">
         <v>135127470</v>
       </c>
-      <c r="E33" s="71">
+      <c r="E33" s="70">
         <v>3450123226</v>
       </c>
       <c r="F33" s="13" t="s">
@@ -4614,10 +4879,10 @@
       <c r="G33" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>45959</v>
       </c>
     </row>
@@ -4628,13 +4893,13 @@
       <c r="B34" s="7">
         <v>45958</v>
       </c>
-      <c r="C34" s="70">
+      <c r="C34" s="69">
         <v>45966</v>
       </c>
       <c r="D34" s="18">
         <v>135127916</v>
       </c>
-      <c r="E34" s="71">
+      <c r="E34" s="70">
         <v>3450123248</v>
       </c>
       <c r="F34" s="13" t="s">
@@ -4643,10 +4908,10 @@
       <c r="G34" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4657,13 +4922,13 @@
       <c r="B35" s="7">
         <v>45958</v>
       </c>
-      <c r="C35" s="70">
+      <c r="C35" s="69">
         <v>45966</v>
       </c>
       <c r="D35" s="18">
         <v>135128652</v>
       </c>
-      <c r="E35" s="73">
+      <c r="E35" s="72">
         <v>3450123260</v>
       </c>
       <c r="F35" s="13" t="s">
@@ -4672,10 +4937,10 @@
       <c r="G35" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4686,13 +4951,13 @@
       <c r="B36" s="7">
         <v>45957</v>
       </c>
-      <c r="C36" s="70">
+      <c r="C36" s="69">
         <v>45966</v>
       </c>
       <c r="D36" s="18">
         <v>135130128</v>
       </c>
-      <c r="E36" s="74">
+      <c r="E36" s="73">
         <v>3450122016</v>
       </c>
       <c r="F36" s="13" t="s">
@@ -4701,10 +4966,10 @@
       <c r="G36" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>45957</v>
       </c>
     </row>
@@ -4715,13 +4980,13 @@
       <c r="B37" s="7">
         <v>45958</v>
       </c>
-      <c r="C37" s="70">
+      <c r="C37" s="69">
         <v>45966</v>
       </c>
       <c r="D37" s="18">
         <v>135134019</v>
       </c>
-      <c r="E37" s="74">
+      <c r="E37" s="73">
         <v>3450123897</v>
       </c>
       <c r="F37" s="13" t="s">
@@ -4730,10 +4995,10 @@
       <c r="G37" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4744,13 +5009,13 @@
       <c r="B38" s="7">
         <v>45958</v>
       </c>
-      <c r="C38" s="70">
+      <c r="C38" s="69">
         <v>45966</v>
       </c>
       <c r="D38" s="18">
         <v>135134249</v>
       </c>
-      <c r="E38" s="74">
+      <c r="E38" s="73">
         <v>3450123930</v>
       </c>
       <c r="F38" s="13" t="s">
@@ -4759,10 +5024,10 @@
       <c r="G38" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>45966</v>
       </c>
     </row>
@@ -4773,13 +5038,13 @@
       <c r="B39" s="7">
         <v>45958</v>
       </c>
-      <c r="C39" s="70">
+      <c r="C39" s="69">
         <v>45966</v>
       </c>
       <c r="D39" s="18">
         <v>135138811</v>
       </c>
-      <c r="E39" s="74">
+      <c r="E39" s="73">
         <v>3450124360</v>
       </c>
       <c r="F39" s="13" t="s">
@@ -4788,10 +5053,10 @@
       <c r="G39" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="H39" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4802,13 +5067,13 @@
       <c r="B40" s="7">
         <v>45958</v>
       </c>
-      <c r="C40" s="70">
+      <c r="C40" s="69">
         <v>45966</v>
       </c>
       <c r="D40" s="18">
         <v>135142007</v>
       </c>
-      <c r="E40" s="74">
+      <c r="E40" s="73">
         <v>3450124690</v>
       </c>
       <c r="F40" s="13" t="s">
@@ -4817,10 +5082,10 @@
       <c r="G40" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="45" t="s">
+      <c r="H40" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4831,13 +5096,13 @@
       <c r="B41" s="7">
         <v>45958</v>
       </c>
-      <c r="C41" s="70">
+      <c r="C41" s="69">
         <v>45966</v>
       </c>
       <c r="D41" s="18">
         <v>135144041</v>
       </c>
-      <c r="E41" s="74">
+      <c r="E41" s="73">
         <v>3450124997</v>
       </c>
       <c r="F41" s="13" t="s">
@@ -4846,10 +5111,10 @@
       <c r="G41" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="43">
         <v>45958</v>
       </c>
     </row>
@@ -4874,7 +5139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4921,631 +5186,1636 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="44">
-        <v>45819</v>
-      </c>
-      <c r="D2" s="60" t="s">
+      <c r="B2" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="18">
         <v>3450126900</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I2" s="25"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="7">
+        <v>45974</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D3" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="64">
+        <v>3450130871</v>
+      </c>
+      <c r="F3" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="44">
-        <v>45819</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="18">
-        <v>3450130871</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" s="25"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D4" s="80">
+        <v>135083025</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450118001</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="43">
+        <v>45953</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D5" s="80">
+        <v>135098394</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450120696</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="43">
+        <v>45954</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D6" s="80">
+        <v>135088866</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450119508</v>
+      </c>
+      <c r="F6" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="43">
+        <v>45954</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D7" s="80">
+        <v>135102415</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450121246</v>
+      </c>
+      <c r="F7" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="I7" s="43">
+        <v>45966</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D8" s="80">
+        <v>135101112</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450121158</v>
+      </c>
+      <c r="F8" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="43">
+        <v>45954</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="25"/>
+      <c r="B9" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D9" s="80">
+        <v>135090154</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450119717</v>
+      </c>
+      <c r="F9" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="43">
+        <v>45954</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D10" s="80">
+        <v>135150017</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450125327</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I10" s="43">
+        <v>45966</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="25"/>
+      <c r="B11" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D11" s="80">
+        <v>135161482</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450126669</v>
+      </c>
+      <c r="F11" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="25"/>
+      <c r="B12" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D12" s="80">
+        <v>135162103</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450126780</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="25"/>
+      <c r="B13" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D13" s="80">
+        <v>135163012</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450126878</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D14" s="80">
+        <v>135163354</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450126922</v>
+      </c>
+      <c r="F14" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="25"/>
+      <c r="B15" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D15" s="80">
+        <v>135164098</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450125239</v>
+      </c>
+      <c r="F15" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="25"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D16" s="80">
+        <v>135147239</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450124007</v>
+      </c>
+      <c r="F16" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="25"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D17" s="80">
+        <v>135148235</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450123622</v>
+      </c>
+      <c r="F17" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="43">
+        <v>45958</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D18" s="80">
+        <v>135152378</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450125525</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D19" s="80">
+        <v>135164538</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450125712</v>
+      </c>
+      <c r="F19" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D20" s="80">
+        <v>135164558</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450125778</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D21" s="80">
+        <v>135164609</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450125976</v>
+      </c>
+      <c r="F21" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D22" s="80">
+        <v>135164739</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450125844</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D23" s="80">
+        <v>135164110</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450126900</v>
+      </c>
+      <c r="F23" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D24" s="80">
+        <v>135159402</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450126471</v>
+      </c>
+      <c r="F24" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D25" s="80">
+        <v>135164485</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450125701</v>
+      </c>
+      <c r="F25" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C26" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D26" s="80">
+        <v>135152474</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450125558</v>
+      </c>
+      <c r="F26" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C27" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D27" s="80">
+        <v>135195509</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450129683</v>
+      </c>
+      <c r="F27" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="I27" s="43">
+        <v>45961</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C28" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D28" s="80">
+        <v>135200528</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450130332</v>
+      </c>
+      <c r="F28" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" s="43">
+        <v>45961</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C29" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D29" s="80">
+        <v>135159146</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450126438</v>
+      </c>
+      <c r="F29" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="43">
+        <v>45959</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C30" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D30" s="80">
+        <v>135218311</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450132334</v>
+      </c>
+      <c r="F30" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" s="43">
+        <v>45966</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C31" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D31" s="80">
+        <v>135215076</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450132048</v>
+      </c>
+      <c r="F31" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I31" s="43">
+        <v>45966</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C32" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D32" s="80">
+        <v>135211128</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450131290</v>
+      </c>
+      <c r="F32" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="43">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C33" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D33" s="80">
+        <v>135230182</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450133192</v>
+      </c>
+      <c r="F33" s="77" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="43">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45953</v>
+      </c>
+      <c r="C34" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D34" s="80">
+        <v>135084424</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450118309</v>
+      </c>
+      <c r="F34" s="77" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="43">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C35" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D35" s="80">
+        <v>135091782</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3450120003</v>
+      </c>
+      <c r="F35" s="77" t="s">
+        <v>194</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C36" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D36" s="80">
+        <v>135094583</v>
+      </c>
+      <c r="E36" s="18">
+        <v>3450120267</v>
+      </c>
+      <c r="F36" s="77" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C37" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D37" s="80">
+        <v>135095572</v>
+      </c>
+      <c r="E37" s="18">
+        <v>3450120377</v>
+      </c>
+      <c r="F37" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C38" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D38" s="80">
+        <v>135097409</v>
+      </c>
+      <c r="E38" s="18">
+        <v>3450120608</v>
+      </c>
+      <c r="F38" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C39" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D39" s="80">
+        <v>135096412</v>
+      </c>
+      <c r="E39" s="18">
+        <v>3450120454</v>
+      </c>
+      <c r="F39" s="77" t="s">
+        <v>198</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C40" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D40" s="80">
+        <v>135096941</v>
+      </c>
+      <c r="E40" s="18">
+        <v>3450120509</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C41" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D41" s="80">
+        <v>135097981</v>
+      </c>
+      <c r="E41" s="18">
+        <v>3450120674</v>
+      </c>
+      <c r="F41" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C42" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D42" s="80">
+        <v>135099100</v>
+      </c>
+      <c r="E42" s="18">
+        <v>3450120806</v>
+      </c>
+      <c r="F42" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C43" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D43" s="80">
+        <v>135099336</v>
+      </c>
+      <c r="E43" s="18">
+        <v>3450120850</v>
+      </c>
+      <c r="F43" s="77" t="s">
+        <v>202</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I43" s="43">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C44" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D44" s="80">
+        <v>135089764</v>
+      </c>
+      <c r="E44" s="18">
+        <v>3450119630</v>
+      </c>
+      <c r="F44" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="I44" s="83">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C45" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D45" s="80">
+        <v>135096062</v>
+      </c>
+      <c r="E45" s="18">
+        <v>3450120400</v>
+      </c>
+      <c r="F45" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="G45" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="83">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="84">
+        <v>45954</v>
+      </c>
+      <c r="C46" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D46" s="81">
+        <v>135091578</v>
+      </c>
+      <c r="E46" s="64">
+        <v>3450119981</v>
+      </c>
+      <c r="F46" s="85" t="s">
+        <v>206</v>
+      </c>
+      <c r="G46" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="83">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="43">
+        <v>45954</v>
+      </c>
+      <c r="C47" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D47" s="80">
+        <v>135101522</v>
+      </c>
+      <c r="E47" s="18">
+        <v>3450121180</v>
+      </c>
+      <c r="F47" s="86" t="s">
+        <v>207</v>
+      </c>
+      <c r="G47" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="92" t="s">
+        <v>208</v>
+      </c>
+      <c r="I47" s="93">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="43">
+        <v>45976</v>
+      </c>
+      <c r="C48" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D48" s="80">
+        <v>135088154</v>
+      </c>
+      <c r="E48" s="18">
+        <v>3450119409</v>
+      </c>
+      <c r="F48" s="86" t="s">
+        <v>209</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I48" s="43">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="43">
+        <v>45964</v>
+      </c>
+      <c r="C49" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D49" s="80">
+        <v>135221699</v>
+      </c>
+      <c r="E49" s="18">
+        <v>3450132686</v>
+      </c>
+      <c r="F49" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G49" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I49" s="43">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C50" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D50" s="80">
+        <v>135148358</v>
+      </c>
+      <c r="E50" s="18">
+        <v>3450125140</v>
+      </c>
+      <c r="F50" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="G50" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="I50" s="94">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C51" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D51" s="80">
+        <v>135153663</v>
+      </c>
+      <c r="E51" s="18">
+        <v>3450125723</v>
+      </c>
+      <c r="F51" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I51" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C52" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D52" s="80">
+        <v>135154592</v>
+      </c>
+      <c r="E52" s="18">
+        <v>3450125811</v>
+      </c>
+      <c r="F52" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I52" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C53" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D53" s="80">
+        <v>135156213</v>
+      </c>
+      <c r="E53" s="18">
+        <v>3450126086</v>
+      </c>
+      <c r="F53" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I53" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C54" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D54" s="80">
+        <v>135157735</v>
+      </c>
+      <c r="E54" s="18">
+        <v>3450126273</v>
+      </c>
+      <c r="F54" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I54" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C55" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D55" s="80">
+        <v>135159289</v>
+      </c>
+      <c r="E55" s="18">
+        <v>3450126450</v>
+      </c>
+      <c r="F55" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I55" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C56" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D56" s="80">
+        <v>135164300</v>
+      </c>
+      <c r="E56" s="18">
+        <v>3450125404</v>
+      </c>
+      <c r="F56" s="77" t="s">
+        <v>218</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I56" s="83">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="43">
+        <v>45959</v>
+      </c>
+      <c r="C57" s="7">
+        <v>45967</v>
+      </c>
+      <c r="D57" s="80">
+        <v>135164486</v>
+      </c>
+      <c r="E57" s="18">
+        <v>3450126317</v>
+      </c>
+      <c r="F57" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I57" s="83">
+        <v>45959</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{5A2669B6-989B-49D6-BBDC-D101598AEC55}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G57" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+      <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A57" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
-      <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{5A2669B6-989B-49D6-BBDC-D101598AEC55}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5619,7 +6889,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="35"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -5652,8 +6922,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="25"/>
@@ -6183,7 +7453,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6199,8 +7469,8 @@
       <c r="D2" s="23"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="36"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="35"/>
       <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9">
@@ -6212,8 +7482,8 @@
       <c r="D3" s="23"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="36"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="35"/>
       <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9">
@@ -6225,8 +7495,8 @@
       <c r="D4" s="23"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="36"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="35"/>
       <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9">
@@ -6238,8 +7508,8 @@
       <c r="D5" s="23"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="37"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9">
@@ -6251,8 +7521,8 @@
       <c r="D6" s="23"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
@@ -6264,8 +7534,8 @@
       <c r="D7" s="23"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="38"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:9">
@@ -6277,8 +7547,8 @@
       <c r="D8" s="23"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="38"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9">
@@ -6290,8 +7560,8 @@
       <c r="D9" s="23"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="36"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:9">
@@ -6303,8 +7573,8 @@
       <c r="D10" s="23"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="25"/>
     </row>
     <row r="11" spans="1:9">
@@ -6316,8 +7586,8 @@
       <c r="D11" s="23"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="36"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="25"/>
     </row>
     <row r="12" spans="1:9">
@@ -6329,8 +7599,8 @@
       <c r="D12" s="23"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="36"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9">
@@ -6342,8 +7612,8 @@
       <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9">
@@ -6355,8 +7625,8 @@
       <c r="D14" s="23"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9">
@@ -6368,8 +7638,8 @@
       <c r="D15" s="23"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="36"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:9">
@@ -6381,12 +7651,12 @@
       <c r="D16" s="23"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="36"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="25"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
@@ -6394,8 +7664,8 @@
       <c r="D17" s="23"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="36"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9">
@@ -6407,8 +7677,8 @@
       <c r="D18" s="23"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="36"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9">
@@ -6416,9 +7686,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="30"/>
       <c r="H19" s="9"/>
       <c r="I19" s="25"/>
     </row>
@@ -6429,7 +7699,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="31"/>
+      <c r="G20" s="30"/>
       <c r="H20" s="9"/>
       <c r="I20" s="25"/>
     </row>
@@ -6440,7 +7710,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="31"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="9"/>
       <c r="I21" s="25"/>
     </row>
@@ -6451,7 +7721,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="9"/>
       <c r="I22" s="25"/>
     </row>
@@ -6462,7 +7732,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="31"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="9"/>
       <c r="I23" s="25"/>
     </row>
@@ -6473,7 +7743,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="31"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="9"/>
       <c r="I24" s="25"/>
     </row>
@@ -7510,53 +8780,46 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517946</Url>
+      <Description>QAFFA7D2F2TC-2102087286-517946</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7938,46 +9201,53 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517946</Url>
-      <Description>QAFFA7D2F2TC-2102087286-517946</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7985,7 +9255,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7993,5 +9263,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 03.11.2025 a 09.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A0A34D-06C1-4C60-B9CE-7DC693712C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{731558E5-0E6A-439A-94F1-ACD8CACFE5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="03.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="286">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -715,6 +715,244 @@
   </si>
   <si>
     <t xml:space="preserve">RAUL QUEIROZ LUCIO DOS SANTOS                </t>
+  </si>
+  <si>
+    <t>Limbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEAN CARLOS GONCALVES DE SOUZA CPF: 09415060611  </t>
+  </si>
+  <si>
+    <t>Nup Cancelamento 06/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HASSAN PARACAT CPF: 06133788909 </t>
+  </si>
+  <si>
+    <t>FABIO DE OLIVEIRA CARVALHO CPF  09477262765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA RIBEIRO CRUZ                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON DULTRA MUNIZ                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO CESAR DA CRUZ                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo em duplicidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO DE LIMA RENO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EWERTON LUCIO DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONCALVES E AGUIAR RESTAURANTE LTDA ME       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE LUIS PAULUCCI                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYLVANA MADALENO DE ARAUJO VIANNA            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) SYLVANA MADALENO DE ARAUJO VIANNA, pois este não consta como c
+ondutor na apólice anterior. &lt;br&gt;Neste caso estamos nesta data ef
+etuando a recusa desta proposta. Orientamos transmitir um novo pro
+cesso comoSeguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALBERTO MARANI                        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEAN CARLOS GONCALVES DE SOUZA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ROBERTO DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATILDE FURUKAWA HORIE                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) MATILDE FURUKAWA HORIE, pois este não consta como condutor na
+apólice anterior. &lt;br&gt;Neste caso estamos nesta data efetuando a r
+ecusa desta proposta. Orientamos transmitir um novo processo como
+Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLAUCIENE DE OLIVEIRA FABRICIO MENESES       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMARA MAGDALA BARBOSA GONCALVES             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRO ZANETTI                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVANA BUDAG BECKER BUBNIAK                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO BARROS DE OLIVEIRA                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) TIAGO BARROS DE OLIVEIRA, pois este não consta como condutor n
+a apólice anterior. &lt;br&gt;Neste caso estamos nesta data efetuando a
+recusa desta proposta. Orientamos transmitir um novo processo com
+o Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA SEAWRIGHT ADORNO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO ITACARAMBI BATISTA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATTIVA COMERCIO LTDA EPP                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não h
+á possibilidade efetuar a transferência de bônus para a empresa AT
+TIVA COMERCIO LTDA EPP, pois o(a) senhor(a) RAFHAELA DA SILVA NERI
+, não consta no quadro de sócios da empresa. &lt;br&gt;Neste caso estam
+os nesta data efetuando a recusa desta proposta. Orientamos transm
+itir um novo processo como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO RAMOS DOS SANTOS                       </t>
+  </si>
+  <si>
+    <t>Devido a alteração para a nova CI, o bônus permanecerá 0 por não t
+er completado 1 ano de vigência, por gentileza nos retornar com o
+de acordo conforme informado anteriormente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ DONIZETI CARNEIRO                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026;&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO CARDOSO DE OLIVEIRA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE DE MATOS ROCHA                         </t>
+  </si>
+  <si>
+    <t>A apólice enviada é de uma seguradora que ainda não faz parte da C
+onfederação Nacional das Seguradoras. Caso o cliente não tenha out
+a apólice será necessario cancelar esta proposta e retransmitir co
+moseguro novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINILSE APARECIDA MORA ARREBOLA FATORETTO  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAUJO CONFECCOES LTDA EPP                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA HELENA BAPTISTA BAIRRAL            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GESY DE LUNA FREIRE SALES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO ROBERGE DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRA SILVANA CANDIDO DOS SANTOS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOVIS MASSEI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATHAN FERREIRA NERI                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ PHILIPE NUNES DE OLIVEIRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARISSA WAGNER FELIX                         </t>
+  </si>
+  <si>
+    <t>46 975 813 LILIANE RODRIGUES DE SOUZA ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do pass, Frente e lateral do mot, Traseira e lateral do pass, Traseira e lateral do mot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMUEL DA SILVA SANCHES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS NORMANN NOVOA PAREDES FILHO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposta em duplicidade&lt;br&gt;&lt;br&gt;Informamos que a pr
+oposta em questão se encontra em duplicidade com uma apólice de ou
+tra corretagem, para prosseguirmos com a emissão se faz necessário
+realizar o cancelamento da mesma. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ ANTONIO MIRANDA                         </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo, Frente e lateral do motorista, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMERO CAMPOS DE SOUZA MOREIRA JUNIOR        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL DO NASCIMENTO SILVA                   </t>
+  </si>
+  <si>
+    <t>IS não encontrada para a Versão/CódFipe/AnoMod.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVELIN FERREIRA POMPEO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia do endosso de cancelamento da apólice 2024/202
+5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAQUELINE FAVARO FERREIRA                    </t>
+  </si>
+  <si>
+    <t>Confirmação de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEOZIANE FERREIRA PINTO                      </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Frente e lateral do motorista, Chassi</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1115,7 +1353,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1173,12 +1410,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1284,15 +1516,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1302,8 +1530,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1311,7 +1538,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1321,6 +1547,37 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1706,25 +1963,25 @@
       <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="25">
         <v>45964</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>3450130190</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="39" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1735,25 +1992,25 @@
       <c r="B3" s="7">
         <v>45966</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>45964</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <v>135123173</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>3450123072</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -1764,25 +2021,25 @@
       <c r="B4" s="7">
         <v>45955</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>45964</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <v>135105244</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>3450121290</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="39">
         <v>45955</v>
       </c>
     </row>
@@ -1793,25 +2050,25 @@
       <c r="B5" s="7">
         <v>45958</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>45964</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <v>135133421</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>3450123743</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -1822,25 +2079,25 @@
       <c r="B6" s="7">
         <v>45958</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>45964</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <v>135140502</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>3450124568</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -1851,25 +2108,25 @@
       <c r="B7" s="7">
         <v>45958</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>45964</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>135137538</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>3450124260</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -1880,25 +2137,25 @@
       <c r="B8" s="7">
         <v>45958</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>45964</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <v>135133617</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>3450123820</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -1909,25 +2166,25 @@
       <c r="B9" s="7">
         <v>45958</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>45964</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <v>135133236</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>3450123699</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="47" t="s">
+      <c r="H9" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -1938,25 +2195,25 @@
       <c r="B10" s="7">
         <v>45959</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>45964</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>135155674</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>3450125998</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -1967,25 +2224,25 @@
       <c r="B11" s="7">
         <v>45959</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>45964</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="22">
         <v>135156059</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>3450126031</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -1996,25 +2253,25 @@
       <c r="B12" s="7">
         <v>45959</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>45964</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="22">
         <v>135155268</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>3450125965</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2025,25 +2282,25 @@
       <c r="B13" s="7">
         <v>45959</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>45964</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="22">
         <v>135156088</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>3450126053</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2054,25 +2311,25 @@
       <c r="B14" s="7">
         <v>45959</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>45964</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <v>135162327</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>3450126801</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2083,25 +2340,25 @@
       <c r="B15" s="7">
         <v>45959</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>45964</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <v>135163700</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>3450126977</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2112,25 +2369,25 @@
       <c r="B16" s="7">
         <v>45959</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>45964</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="22">
         <v>135154363</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>3450125790</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2141,25 +2398,25 @@
       <c r="B17" s="7">
         <v>45959</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>45964</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <v>135164544</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>3450126185</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2170,25 +2427,25 @@
       <c r="B18" s="7">
         <v>45959</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>45964</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <v>135159061</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>3450126427</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2199,25 +2456,25 @@
       <c r="B19" s="7">
         <v>45959</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <v>45964</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <v>135154636</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>3450125833</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -2228,25 +2485,25 @@
       <c r="B20" s="7">
         <v>45972</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>45964</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="22">
         <v>135146609</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>3450125030</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="39">
         <v>45972</v>
       </c>
     </row>
@@ -2257,25 +2514,25 @@
       <c r="B21" s="7">
         <v>45960</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>45964</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <v>135174779</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>3450127880</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="52" t="s">
+      <c r="G21" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="53">
+      <c r="I21" s="49">
         <v>45960</v>
       </c>
     </row>
@@ -2286,25 +2543,25 @@
       <c r="B22" s="7">
         <v>45958</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>45964</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <v>135129415</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>3450123336</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="F22" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="51" t="s">
+      <c r="G22" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -2315,25 +2572,25 @@
       <c r="B23" s="7">
         <v>45980</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <v>45964</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>135171249</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <v>3450127439</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2344,25 +2601,25 @@
       <c r="B24" s="7">
         <v>45960</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>45964</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>135168476</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <v>3450127153</v>
       </c>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G24" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -2373,25 +2630,25 @@
       <c r="B25" s="7">
         <v>45960</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="25">
         <v>45964</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <v>135176940</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="17">
         <v>3450128000</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -2402,25 +2659,25 @@
       <c r="B26" s="7">
         <v>45960</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="25">
         <v>45964</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="22">
         <v>135180725</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="17">
         <v>3450128418</v>
       </c>
-      <c r="F26" s="46" t="s">
+      <c r="F26" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="39">
         <v>45964</v>
       </c>
     </row>
@@ -2431,25 +2688,25 @@
       <c r="B27" s="7">
         <v>45961</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="25">
         <v>45964</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <v>135193358</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="17">
         <v>3450129485</v>
       </c>
-      <c r="F27" s="46" t="s">
+      <c r="F27" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="51" t="s">
+      <c r="G27" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2460,25 +2717,25 @@
       <c r="B28" s="7">
         <v>45961</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="25">
         <v>45964</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <v>135191401</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="17">
         <v>3450129166</v>
       </c>
-      <c r="F28" s="46" t="s">
+      <c r="F28" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="51" t="s">
+      <c r="G28" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2489,25 +2746,25 @@
       <c r="B29" s="7">
         <v>45961</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="25">
         <v>45964</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <v>135200685</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="17">
         <v>3450130376</v>
       </c>
-      <c r="F29" s="46" t="s">
+      <c r="F29" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="51" t="s">
+      <c r="G29" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2518,25 +2775,25 @@
       <c r="B30" s="7">
         <v>45958</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="25">
         <v>45964</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <v>135133426</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="17">
         <v>3450123754</v>
       </c>
-      <c r="F30" s="46" t="s">
+      <c r="F30" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="51" t="s">
+      <c r="G30" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -2547,25 +2804,25 @@
       <c r="B31" s="7">
         <v>45958</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="25">
         <v>45964</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="22">
         <v>135139336</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="17">
         <v>3450124425</v>
       </c>
-      <c r="F31" s="46" t="s">
+      <c r="F31" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -2576,25 +2833,25 @@
       <c r="B32" s="7">
         <v>45954</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="25">
         <v>45964</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="22">
         <v>135110534</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="17">
         <v>3450120290</v>
       </c>
-      <c r="F32" s="46" t="s">
+      <c r="F32" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="51" t="s">
+      <c r="G32" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -2605,25 +2862,25 @@
       <c r="B33" s="7">
         <v>45954</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="25">
         <v>45964</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="22">
         <v>135100251</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="17">
         <v>3450121004</v>
       </c>
-      <c r="F33" s="46" t="s">
+      <c r="F33" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="G33" s="51" t="s">
+      <c r="G33" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="H33" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -2634,25 +2891,25 @@
       <c r="B34" s="7">
         <v>45957</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="25">
         <v>45964</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <v>135116743</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="17">
         <v>3450122313</v>
       </c>
-      <c r="F34" s="46" t="s">
+      <c r="F34" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="51" t="s">
+      <c r="G34" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="39">
         <v>45957</v>
       </c>
     </row>
@@ -2663,101 +2920,101 @@
       <c r="B35" s="7">
         <v>45957</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="25">
         <v>45964</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <v>135111233</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="17">
         <v>3450121642</v>
       </c>
-      <c r="F35" s="46" t="s">
+      <c r="F35" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="39">
         <v>45961</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="20"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="19"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="25"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="21"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="25"/>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="21"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="25"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="20"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="25"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="20"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19"/>
       <c r="H41" s="9"/>
-      <c r="I41" s="25"/>
+      <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="15"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="14"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
     </row>
@@ -2927,12 +3184,12 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2965,58 +3222,58 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="43">
+      <c r="A2" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="39">
         <v>45964</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="39">
         <v>45965</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>3450132246</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="52">
         <v>45964</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="53">
         <v>45965</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>3450131520</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="H3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -3025,25 +3282,25 @@
       <c r="B4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>45965</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="55">
         <v>135057851</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>3450117429</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="F4" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="52">
         <v>45952</v>
       </c>
     </row>
@@ -3054,22 +3311,22 @@
       <c r="B5" s="7">
         <v>45959</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>45965</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="55">
         <v>135051461</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>3450116714</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="40" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="7">
@@ -3083,22 +3340,22 @@
       <c r="B6" s="7">
         <v>45952</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>45965</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="55">
         <v>135051444</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>3450116703</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="41" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="7">
@@ -3112,22 +3369,22 @@
       <c r="B7" s="7">
         <v>45952</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>45965</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="55">
         <v>135043044</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>3450115746</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="F7" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="42" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="7">
@@ -3141,22 +3398,22 @@
       <c r="B8" s="7">
         <v>45952</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>45965</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="55">
         <v>135044605</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>3450115856</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="43" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="7">
@@ -3170,22 +3427,22 @@
       <c r="B9" s="7">
         <v>45952</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>45965</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="55">
         <v>135048417</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>3450116197</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="7">
@@ -3199,22 +3456,22 @@
       <c r="B10" s="7">
         <v>45952</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>45965</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="55">
         <v>135049114</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>3450116351</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I10" s="7">
@@ -3228,22 +3485,22 @@
       <c r="B11" s="7">
         <v>45952</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>45965</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="55">
         <v>135049373</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>3450116373</v>
       </c>
-      <c r="F11" s="60" t="s">
+      <c r="F11" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="7">
@@ -3257,22 +3514,22 @@
       <c r="B12" s="7">
         <v>45952</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>45965</v>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="55">
         <v>135051429</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>3450116681</v>
       </c>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="7">
@@ -3286,22 +3543,22 @@
       <c r="B13" s="7">
         <v>45952</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>45965</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="55">
         <v>135051570</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>3450116725</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="7">
@@ -3315,22 +3572,22 @@
       <c r="B14" s="7">
         <v>45952</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>45965</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="55">
         <v>135056953</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>3450117253</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="7">
@@ -3344,22 +3601,22 @@
       <c r="B15" s="7">
         <v>45952</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>45965</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="55">
         <v>135057252</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>3450117352</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="7">
@@ -3373,22 +3630,22 @@
       <c r="B16" s="7">
         <v>45952</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>45965</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="55">
         <v>135057776</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>3450117418</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I16" s="7">
@@ -3402,22 +3659,22 @@
       <c r="B17" s="7">
         <v>45952</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>45965</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="55">
         <v>135059630</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>3450117649</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="7">
@@ -3431,22 +3688,22 @@
       <c r="B18" s="7">
         <v>45952</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>45965</v>
       </c>
-      <c r="D18" s="59">
+      <c r="D18" s="55">
         <v>135059784</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>3450117682</v>
       </c>
-      <c r="F18" s="60" t="s">
+      <c r="F18" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="7">
@@ -3460,22 +3717,22 @@
       <c r="B19" s="7">
         <v>45952</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <v>45965</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="55">
         <v>135061235</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>3450117759</v>
       </c>
-      <c r="F19" s="60" t="s">
+      <c r="F19" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="7">
@@ -3489,22 +3746,22 @@
       <c r="B20" s="7">
         <v>45952</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>45965</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="55">
         <v>135055840</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>3450117110</v>
       </c>
-      <c r="F20" s="60" t="s">
+      <c r="F20" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="40" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="7">
@@ -3514,156 +3771,156 @@
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="19"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="25"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="19"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="25"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="19"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="25"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="19"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="25"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="25"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="19"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="25"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="19"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="25"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="19"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="25"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="25"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="25"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="25"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="14"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="25"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -3674,7 +3931,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="25"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -3685,7 +3942,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="25"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -3919,14 +4176,14 @@
   <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="25" customWidth="1"/>
+    <col min="9" max="9" width="21" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3954,36 +4211,36 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="25">
         <v>45965</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="39">
         <v>45966</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="60">
         <v>3450134402</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="39" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3991,86 +4248,86 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="25">
         <v>45953</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="39">
         <v>45966</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="70">
         <v>135076900</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>3450118848</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="H3" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="39">
         <v>45966</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="26">
+      <c r="A4" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="25">
         <v>45954</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="65">
         <v>45966</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>135099564</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="66">
         <v>3450120905</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="53">
+      <c r="I4" s="49">
         <v>45965</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="75">
+      <c r="A5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="71">
         <v>45957</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="65">
         <v>45966</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>135128663</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="67">
         <v>3450122775</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="39">
         <v>45957</v>
       </c>
     </row>
@@ -4078,28 +4335,28 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="72">
         <v>45957</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="65">
         <v>45966</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>135128447</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="66">
         <v>3450122797</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4107,28 +4364,28 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="72">
         <v>45958</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="65">
         <v>45966</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>135136881</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="66">
         <v>3450124172</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4136,28 +4393,28 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="72">
         <v>45958</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="65">
         <v>45966</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>135139953</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="66">
         <v>3450124513</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -4165,28 +4422,28 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="72">
         <v>45958</v>
       </c>
-      <c r="C9" s="69">
+      <c r="C9" s="65">
         <v>45966</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>135141304</v>
       </c>
-      <c r="E9" s="70">
+      <c r="E9" s="66">
         <v>3450124645</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4194,28 +4451,28 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="72">
         <v>45958</v>
       </c>
-      <c r="C10" s="69">
+      <c r="C10" s="65">
         <v>45966</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>135135779</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="66">
         <v>3450124106</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4223,28 +4480,28 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="72">
         <v>45958</v>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="65">
         <v>45966</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>135143557</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="66">
         <v>3450124910</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4252,28 +4509,28 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="72">
         <v>45959</v>
       </c>
-      <c r="C12" s="69">
+      <c r="C12" s="65">
         <v>45966</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>135163415</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="66">
         <v>3450126933</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4281,28 +4538,28 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="76">
+      <c r="B13" s="72">
         <v>45958</v>
       </c>
-      <c r="C13" s="69">
+      <c r="C13" s="65">
         <v>45966</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>135144707</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="66">
         <v>3450125020</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4310,28 +4567,28 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="76">
+      <c r="B14" s="72">
         <v>45960</v>
       </c>
-      <c r="C14" s="69">
+      <c r="C14" s="65">
         <v>45966</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>135167327</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="66">
         <v>3450127076</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -4339,28 +4596,28 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="76">
+      <c r="B15" s="72">
         <v>45958</v>
       </c>
-      <c r="C15" s="69">
+      <c r="C15" s="65">
         <v>45966</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <v>135142892</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="66">
         <v>3450124799</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4368,28 +4625,28 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="76">
+      <c r="B16" s="72">
         <v>45960</v>
       </c>
-      <c r="C16" s="69">
+      <c r="C16" s="65">
         <v>45966</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>135169853</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="66">
         <v>3450127263</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -4397,28 +4654,28 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="76">
+      <c r="B17" s="72">
         <v>45960</v>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="65">
         <v>45966</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>135175287</v>
       </c>
-      <c r="E17" s="70">
+      <c r="E17" s="66">
         <v>3450127945</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -4426,28 +4683,28 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="76">
+      <c r="B18" s="72">
         <v>45961</v>
       </c>
-      <c r="C18" s="69">
+      <c r="C18" s="65">
         <v>45966</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>135196667</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="66">
         <v>3450129793</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -4455,28 +4712,28 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="76">
+      <c r="B19" s="72">
         <v>45961</v>
       </c>
-      <c r="C19" s="69">
+      <c r="C19" s="65">
         <v>45966</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>135198665</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="66">
         <v>3450130134</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -4484,28 +4741,28 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="76">
+      <c r="B20" s="72">
         <v>45961</v>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="65">
         <v>45966</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <v>135189146</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="66">
         <v>3450128902</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -4513,28 +4770,28 @@
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="76">
+      <c r="B21" s="72">
         <v>45961</v>
       </c>
-      <c r="C21" s="69">
+      <c r="C21" s="65">
         <v>45966</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>135196535</v>
       </c>
-      <c r="E21" s="70">
+      <c r="E21" s="66">
         <v>3450129760</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -4542,28 +4799,28 @@
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="76">
+      <c r="B22" s="72">
         <v>45959</v>
       </c>
-      <c r="C22" s="69">
+      <c r="C22" s="65">
         <v>45966</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <v>135162952</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="66">
         <v>3450126856</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4571,28 +4828,28 @@
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="76">
+      <c r="B23" s="72">
         <v>45964</v>
       </c>
-      <c r="C23" s="69">
+      <c r="C23" s="65">
         <v>45966</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="17">
         <v>135217292</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="66">
         <v>3450132257</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="39">
         <v>45964</v>
       </c>
     </row>
@@ -4600,28 +4857,28 @@
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="76">
+      <c r="B24" s="72">
         <v>45978</v>
       </c>
-      <c r="C24" s="69">
+      <c r="C24" s="65">
         <v>45966</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="17">
         <v>135221235</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="66">
         <v>3450132708</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4629,28 +4886,28 @@
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="72">
         <v>45969</v>
       </c>
-      <c r="C25" s="69">
+      <c r="C25" s="65">
         <v>45966</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="17">
         <v>135213060</v>
       </c>
-      <c r="E25" s="70">
+      <c r="E25" s="66">
         <v>3450131685</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="39">
         <v>45969</v>
       </c>
     </row>
@@ -4658,28 +4915,28 @@
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="76">
+      <c r="B26" s="72">
         <v>45969</v>
       </c>
-      <c r="C26" s="69">
+      <c r="C26" s="65">
         <v>45966</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="17">
         <v>135211114</v>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="66">
         <v>3450131289</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4687,28 +4944,28 @@
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="76">
+      <c r="B27" s="72">
         <v>45954</v>
       </c>
-      <c r="C27" s="69">
+      <c r="C27" s="65">
         <v>45966</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="17">
         <v>135099857</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E27" s="66">
         <v>3450120938</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4716,28 +4973,28 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="76">
+      <c r="B28" s="72">
         <v>45953</v>
       </c>
-      <c r="C28" s="69">
+      <c r="C28" s="65">
         <v>45966</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="17">
         <v>135083116</v>
       </c>
-      <c r="E28" s="70">
+      <c r="E28" s="66">
         <v>3450118056</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4745,28 +5002,28 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="76">
+      <c r="B29" s="72">
         <v>45972</v>
       </c>
-      <c r="C29" s="69">
+      <c r="C29" s="65">
         <v>45966</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="17">
         <v>135148512</v>
       </c>
-      <c r="E29" s="70">
+      <c r="E29" s="66">
         <v>3450125151</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -4774,28 +5031,28 @@
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="76">
+      <c r="B30" s="72">
         <v>45953</v>
       </c>
-      <c r="C30" s="69">
+      <c r="C30" s="65">
         <v>45966</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="17">
         <v>135069472</v>
       </c>
-      <c r="E30" s="70">
+      <c r="E30" s="66">
         <v>3450118254</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="44" t="s">
+      <c r="H30" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -4803,28 +5060,28 @@
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="76">
+      <c r="B31" s="72">
         <v>45960</v>
       </c>
-      <c r="C31" s="69">
+      <c r="C31" s="65">
         <v>45966</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="17">
         <v>135177588</v>
       </c>
-      <c r="E31" s="70">
+      <c r="E31" s="66">
         <v>3450128033</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="39">
         <v>45960</v>
       </c>
     </row>
@@ -4835,25 +5092,25 @@
       <c r="B32" s="7">
         <v>45961</v>
       </c>
-      <c r="C32" s="69">
+      <c r="C32" s="65">
         <v>45966</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="17">
         <v>135198288</v>
       </c>
-      <c r="E32" s="70">
+      <c r="E32" s="66">
         <v>3450130046</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -4864,25 +5121,25 @@
       <c r="B33" s="7">
         <v>45958</v>
       </c>
-      <c r="C33" s="69">
+      <c r="C33" s="65">
         <v>45966</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="17">
         <v>135127470</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E33" s="66">
         <v>3450123226</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -4893,25 +5150,25 @@
       <c r="B34" s="7">
         <v>45958</v>
       </c>
-      <c r="C34" s="69">
+      <c r="C34" s="65">
         <v>45966</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="17">
         <v>135127916</v>
       </c>
-      <c r="E34" s="70">
+      <c r="E34" s="66">
         <v>3450123248</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4922,25 +5179,25 @@
       <c r="B35" s="7">
         <v>45958</v>
       </c>
-      <c r="C35" s="69">
+      <c r="C35" s="65">
         <v>45966</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="17">
         <v>135128652</v>
       </c>
-      <c r="E35" s="72">
+      <c r="E35" s="68">
         <v>3450123260</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -4951,25 +5208,25 @@
       <c r="B36" s="7">
         <v>45957</v>
       </c>
-      <c r="C36" s="69">
+      <c r="C36" s="65">
         <v>45966</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="17">
         <v>135130128</v>
       </c>
-      <c r="E36" s="73">
+      <c r="E36" s="69">
         <v>3450122016</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H36" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="39">
         <v>45957</v>
       </c>
     </row>
@@ -4980,25 +5237,25 @@
       <c r="B37" s="7">
         <v>45958</v>
       </c>
-      <c r="C37" s="69">
+      <c r="C37" s="65">
         <v>45966</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="17">
         <v>135134019</v>
       </c>
-      <c r="E37" s="73">
+      <c r="E37" s="69">
         <v>3450123897</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5009,25 +5266,25 @@
       <c r="B38" s="7">
         <v>45958</v>
       </c>
-      <c r="C38" s="69">
+      <c r="C38" s="65">
         <v>45966</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="17">
         <v>135134249</v>
       </c>
-      <c r="E38" s="73">
+      <c r="E38" s="69">
         <v>3450123930</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -5038,25 +5295,25 @@
       <c r="B39" s="7">
         <v>45958</v>
       </c>
-      <c r="C39" s="69">
+      <c r="C39" s="65">
         <v>45966</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="17">
         <v>135138811</v>
       </c>
-      <c r="E39" s="73">
+      <c r="E39" s="69">
         <v>3450124360</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5067,25 +5324,25 @@
       <c r="B40" s="7">
         <v>45958</v>
       </c>
-      <c r="C40" s="69">
+      <c r="C40" s="65">
         <v>45966</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="17">
         <v>135142007</v>
       </c>
-      <c r="E40" s="73">
+      <c r="E40" s="69">
         <v>3450124690</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="44" t="s">
+      <c r="H40" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5096,25 +5353,25 @@
       <c r="B41" s="7">
         <v>45958</v>
       </c>
-      <c r="C41" s="69">
+      <c r="C41" s="65">
         <v>45966</v>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="17">
         <v>135144041</v>
       </c>
-      <c r="E41" s="73">
+      <c r="E41" s="69">
         <v>3450124997</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5192,22 +5449,22 @@
       <c r="C2" s="7">
         <v>45967</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>3450126900</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -5219,22 +5476,22 @@
       <c r="C3" s="7">
         <v>45967</v>
       </c>
-      <c r="D3" s="78" t="s">
+      <c r="D3" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="60">
         <v>3450130871</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -5246,22 +5503,22 @@
       <c r="C4" s="7">
         <v>45967</v>
       </c>
-      <c r="D4" s="80">
+      <c r="D4" s="22">
         <v>135083025</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>3450118001</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -5275,22 +5532,22 @@
       <c r="C5" s="7">
         <v>45967</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="22">
         <v>135098394</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>3450120696</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -5304,22 +5561,22 @@
       <c r="C6" s="7">
         <v>45967</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="22">
         <v>135088866</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>3450119508</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -5333,22 +5590,22 @@
       <c r="C7" s="7">
         <v>45967</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="22">
         <v>135102415</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>3450121246</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -5362,22 +5619,22 @@
       <c r="C8" s="7">
         <v>45967</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="22">
         <v>135101112</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>3450121158</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -5391,22 +5648,22 @@
       <c r="C9" s="7">
         <v>45967</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="22">
         <v>135090154</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>3450119717</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -5420,22 +5677,22 @@
       <c r="C10" s="7">
         <v>45967</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="22">
         <v>135150017</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>3450125327</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -5449,22 +5706,22 @@
       <c r="C11" s="7">
         <v>45967</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="22">
         <v>135161482</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>3450126669</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5478,22 +5735,22 @@
       <c r="C12" s="7">
         <v>45967</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="22">
         <v>135162103</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>3450126780</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5507,22 +5764,22 @@
       <c r="C13" s="7">
         <v>45967</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="22">
         <v>135163012</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>3450126878</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5536,22 +5793,22 @@
       <c r="C14" s="7">
         <v>45967</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="22">
         <v>135163354</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>3450126922</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5565,22 +5822,22 @@
       <c r="C15" s="7">
         <v>45967</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="22">
         <v>135164098</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>3450125239</v>
       </c>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5594,22 +5851,22 @@
       <c r="C16" s="7">
         <v>45967</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="22">
         <v>135147239</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>3450124007</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5623,22 +5880,22 @@
       <c r="C17" s="7">
         <v>45967</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="22">
         <v>135148235</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>3450123622</v>
       </c>
-      <c r="F17" s="77" t="s">
+      <c r="F17" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -5652,22 +5909,22 @@
       <c r="C18" s="7">
         <v>45967</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="22">
         <v>135152378</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>3450125525</v>
       </c>
-      <c r="F18" s="77" t="s">
+      <c r="F18" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5681,22 +5938,22 @@
       <c r="C19" s="7">
         <v>45967</v>
       </c>
-      <c r="D19" s="80">
+      <c r="D19" s="22">
         <v>135164538</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>3450125712</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5710,22 +5967,22 @@
       <c r="C20" s="7">
         <v>45967</v>
       </c>
-      <c r="D20" s="80">
+      <c r="D20" s="22">
         <v>135164558</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>3450125778</v>
       </c>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5739,22 +5996,22 @@
       <c r="C21" s="7">
         <v>45967</v>
       </c>
-      <c r="D21" s="80">
+      <c r="D21" s="22">
         <v>135164609</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>3450125976</v>
       </c>
-      <c r="F21" s="77" t="s">
+      <c r="F21" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="39">
         <v>45989</v>
       </c>
     </row>
@@ -5768,22 +6025,22 @@
       <c r="C22" s="7">
         <v>45967</v>
       </c>
-      <c r="D22" s="80">
+      <c r="D22" s="22">
         <v>135164739</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>3450125844</v>
       </c>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5797,22 +6054,22 @@
       <c r="C23" s="7">
         <v>45967</v>
       </c>
-      <c r="D23" s="80">
+      <c r="D23" s="22">
         <v>135164110</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <v>3450126900</v>
       </c>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5826,22 +6083,22 @@
       <c r="C24" s="7">
         <v>45967</v>
       </c>
-      <c r="D24" s="80">
+      <c r="D24" s="22">
         <v>135159402</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <v>3450126471</v>
       </c>
-      <c r="F24" s="77" t="s">
+      <c r="F24" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5855,22 +6112,22 @@
       <c r="C25" s="7">
         <v>45967</v>
       </c>
-      <c r="D25" s="80">
+      <c r="D25" s="22">
         <v>135164485</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="17">
         <v>3450125701</v>
       </c>
-      <c r="F25" s="77" t="s">
+      <c r="F25" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5884,22 +6141,22 @@
       <c r="C26" s="7">
         <v>45967</v>
       </c>
-      <c r="D26" s="80">
+      <c r="D26" s="22">
         <v>135152474</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="17">
         <v>3450125558</v>
       </c>
-      <c r="F26" s="77" t="s">
+      <c r="F26" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -5913,22 +6170,22 @@
       <c r="C27" s="7">
         <v>45967</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="22">
         <v>135195509</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="17">
         <v>3450129683</v>
       </c>
-      <c r="F27" s="77" t="s">
+      <c r="F27" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -5942,22 +6199,22 @@
       <c r="C28" s="7">
         <v>45967</v>
       </c>
-      <c r="D28" s="80">
+      <c r="D28" s="22">
         <v>135200528</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="17">
         <v>3450130332</v>
       </c>
-      <c r="F28" s="77" t="s">
+      <c r="F28" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="39">
         <v>45961</v>
       </c>
     </row>
@@ -5971,22 +6228,22 @@
       <c r="C29" s="7">
         <v>45967</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="22">
         <v>135159146</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="17">
         <v>3450126438</v>
       </c>
-      <c r="F29" s="77" t="s">
+      <c r="F29" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="39">
         <v>45959</v>
       </c>
     </row>
@@ -6000,22 +6257,22 @@
       <c r="C30" s="7">
         <v>45967</v>
       </c>
-      <c r="D30" s="80">
+      <c r="D30" s="22">
         <v>135218311</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="17">
         <v>3450132334</v>
       </c>
-      <c r="F30" s="77" t="s">
+      <c r="F30" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H30" s="44" t="s">
+      <c r="H30" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -6029,22 +6286,22 @@
       <c r="C31" s="7">
         <v>45967</v>
       </c>
-      <c r="D31" s="80">
+      <c r="D31" s="22">
         <v>135215076</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="17">
         <v>3450132048</v>
       </c>
-      <c r="F31" s="77" t="s">
+      <c r="F31" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -6058,22 +6315,22 @@
       <c r="C32" s="7">
         <v>45967</v>
       </c>
-      <c r="D32" s="80">
+      <c r="D32" s="22">
         <v>135211128</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="17">
         <v>3450131290</v>
       </c>
-      <c r="F32" s="77" t="s">
+      <c r="F32" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H32" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="39">
         <v>45966</v>
       </c>
     </row>
@@ -6087,22 +6344,22 @@
       <c r="C33" s="7">
         <v>45967</v>
       </c>
-      <c r="D33" s="80">
+      <c r="D33" s="22">
         <v>135230182</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="17">
         <v>3450133192</v>
       </c>
-      <c r="F33" s="77" t="s">
+      <c r="F33" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="39">
         <v>45965</v>
       </c>
     </row>
@@ -6116,22 +6373,22 @@
       <c r="C34" s="7">
         <v>45967</v>
       </c>
-      <c r="D34" s="80">
+      <c r="D34" s="22">
         <v>135084424</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="17">
         <v>3450118309</v>
       </c>
-      <c r="F34" s="77" t="s">
+      <c r="F34" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="44" t="s">
+      <c r="H34" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="39">
         <v>45953</v>
       </c>
     </row>
@@ -6145,22 +6402,22 @@
       <c r="C35" s="7">
         <v>45967</v>
       </c>
-      <c r="D35" s="80">
+      <c r="D35" s="22">
         <v>135091782</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="17">
         <v>3450120003</v>
       </c>
-      <c r="F35" s="77" t="s">
+      <c r="F35" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6174,22 +6431,22 @@
       <c r="C36" s="7">
         <v>45967</v>
       </c>
-      <c r="D36" s="80">
+      <c r="D36" s="22">
         <v>135094583</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="17">
         <v>3450120267</v>
       </c>
-      <c r="F36" s="77" t="s">
+      <c r="F36" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="G36" s="20" t="s">
+      <c r="G36" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H36" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6203,22 +6460,22 @@
       <c r="C37" s="7">
         <v>45967</v>
       </c>
-      <c r="D37" s="80">
+      <c r="D37" s="22">
         <v>135095572</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="17">
         <v>3450120377</v>
       </c>
-      <c r="F37" s="77" t="s">
+      <c r="F37" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6232,22 +6489,22 @@
       <c r="C38" s="7">
         <v>45967</v>
       </c>
-      <c r="D38" s="80">
+      <c r="D38" s="22">
         <v>135097409</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="17">
         <v>3450120608</v>
       </c>
-      <c r="F38" s="77" t="s">
+      <c r="F38" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6261,22 +6518,22 @@
       <c r="C39" s="7">
         <v>45967</v>
       </c>
-      <c r="D39" s="80">
+      <c r="D39" s="22">
         <v>135096412</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="17">
         <v>3450120454</v>
       </c>
-      <c r="F39" s="77" t="s">
+      <c r="F39" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6290,22 +6547,22 @@
       <c r="C40" s="7">
         <v>45967</v>
       </c>
-      <c r="D40" s="80">
+      <c r="D40" s="22">
         <v>135096941</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="17">
         <v>3450120509</v>
       </c>
-      <c r="F40" s="77" t="s">
+      <c r="F40" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="44" t="s">
+      <c r="H40" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6319,22 +6576,22 @@
       <c r="C41" s="7">
         <v>45967</v>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="22">
         <v>135097981</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="17">
         <v>3450120674</v>
       </c>
-      <c r="F41" s="77" t="s">
+      <c r="F41" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6348,22 +6605,22 @@
       <c r="C42" s="7">
         <v>45967</v>
       </c>
-      <c r="D42" s="80">
+      <c r="D42" s="22">
         <v>135099100</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="17">
         <v>3450120806</v>
       </c>
-      <c r="F42" s="77" t="s">
+      <c r="F42" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6377,22 +6634,22 @@
       <c r="C43" s="7">
         <v>45967</v>
       </c>
-      <c r="D43" s="80">
+      <c r="D43" s="22">
         <v>135099336</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="17">
         <v>3450120850</v>
       </c>
-      <c r="F43" s="77" t="s">
+      <c r="F43" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="45" t="s">
+      <c r="H43" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="39">
         <v>45954</v>
       </c>
     </row>
@@ -6406,22 +6663,22 @@
       <c r="C44" s="7">
         <v>45967</v>
       </c>
-      <c r="D44" s="80">
+      <c r="D44" s="22">
         <v>135089764</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="17">
         <v>3450119630</v>
       </c>
-      <c r="F44" s="77" t="s">
+      <c r="F44" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="82" t="s">
+      <c r="H44" s="76" t="s">
         <v>204</v>
       </c>
-      <c r="I44" s="83">
+      <c r="I44" s="77">
         <v>45967</v>
       </c>
     </row>
@@ -6435,22 +6692,22 @@
       <c r="C45" s="7">
         <v>45967</v>
       </c>
-      <c r="D45" s="80">
+      <c r="D45" s="22">
         <v>135096062</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="17">
         <v>3450120400</v>
       </c>
-      <c r="F45" s="77" t="s">
+      <c r="F45" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="G45" s="87" t="s">
+      <c r="G45" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H45" s="88" t="s">
+      <c r="H45" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="I45" s="83">
+      <c r="I45" s="77">
         <v>45954</v>
       </c>
     </row>
@@ -6458,28 +6715,28 @@
       <c r="A46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="84">
+      <c r="B46" s="78">
         <v>45954</v>
       </c>
       <c r="C46" s="7">
         <v>45967</v>
       </c>
-      <c r="D46" s="81">
+      <c r="D46" s="75">
         <v>135091578</v>
       </c>
-      <c r="E46" s="64">
+      <c r="E46" s="60">
         <v>3450119981</v>
       </c>
-      <c r="F46" s="85" t="s">
+      <c r="F46" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="G46" s="51" t="s">
+      <c r="G46" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="82" t="s">
+      <c r="H46" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="I46" s="83">
+      <c r="I46" s="77">
         <v>45954</v>
       </c>
     </row>
@@ -6487,28 +6744,28 @@
       <c r="A47" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="43">
+      <c r="B47" s="39">
         <v>45954</v>
       </c>
       <c r="C47" s="7">
         <v>45967</v>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="22">
         <v>135101522</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="17">
         <v>3450121180</v>
       </c>
-      <c r="F47" s="86" t="s">
+      <c r="F47" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="G47" s="91" t="s">
+      <c r="G47" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="H47" s="92" t="s">
+      <c r="H47" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="I47" s="93">
+      <c r="I47" s="85">
         <v>45967</v>
       </c>
     </row>
@@ -6516,28 +6773,28 @@
       <c r="A48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="43">
+      <c r="B48" s="39">
         <v>45976</v>
       </c>
       <c r="C48" s="7">
         <v>45967</v>
       </c>
-      <c r="D48" s="80">
+      <c r="D48" s="22">
         <v>135088154</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="17">
         <v>3450119409</v>
       </c>
-      <c r="F48" s="86" t="s">
+      <c r="F48" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="G48" s="51" t="s">
+      <c r="G48" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="90" t="s">
+      <c r="H48" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="39">
         <v>45958</v>
       </c>
     </row>
@@ -6545,28 +6802,28 @@
       <c r="A49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="43">
+      <c r="B49" s="39">
         <v>45964</v>
       </c>
       <c r="C49" s="7">
         <v>45967</v>
       </c>
-      <c r="D49" s="80">
+      <c r="D49" s="22">
         <v>135221699</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="17">
         <v>3450132686</v>
       </c>
-      <c r="F49" s="86" t="s">
+      <c r="F49" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="G49" s="51" t="s">
+      <c r="G49" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="H49" s="13" t="s">
+      <c r="H49" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="39">
         <v>45967</v>
       </c>
     </row>
@@ -6574,28 +6831,28 @@
       <c r="A50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="43">
+      <c r="B50" s="39">
         <v>45959</v>
       </c>
       <c r="C50" s="7">
         <v>45967</v>
       </c>
-      <c r="D50" s="80">
+      <c r="D50" s="22">
         <v>135148358</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="17">
         <v>3450125140</v>
       </c>
-      <c r="F50" s="77" t="s">
+      <c r="F50" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G50" s="89" t="s">
+      <c r="G50" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="33" t="s">
+      <c r="H50" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="I50" s="94">
+      <c r="I50" s="86">
         <v>45959</v>
       </c>
     </row>
@@ -6603,28 +6860,28 @@
       <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="43">
+      <c r="B51" s="39">
         <v>45959</v>
       </c>
       <c r="C51" s="7">
         <v>45967</v>
       </c>
-      <c r="D51" s="80">
+      <c r="D51" s="22">
         <v>135153663</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="17">
         <v>3450125723</v>
       </c>
-      <c r="F51" s="77" t="s">
+      <c r="F51" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H51" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I51" s="83">
+      <c r="I51" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6632,28 +6889,28 @@
       <c r="A52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="43">
+      <c r="B52" s="39">
         <v>45959</v>
       </c>
       <c r="C52" s="7">
         <v>45967</v>
       </c>
-      <c r="D52" s="80">
+      <c r="D52" s="22">
         <v>135154592</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="17">
         <v>3450125811</v>
       </c>
-      <c r="F52" s="77" t="s">
+      <c r="F52" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G52" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I52" s="83">
+      <c r="I52" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6661,28 +6918,28 @@
       <c r="A53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="43">
+      <c r="B53" s="39">
         <v>45959</v>
       </c>
       <c r="C53" s="7">
         <v>45967</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="22">
         <v>135156213</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="17">
         <v>3450126086</v>
       </c>
-      <c r="F53" s="77" t="s">
+      <c r="F53" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="G53" s="24" t="s">
+      <c r="G53" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I53" s="83">
+      <c r="I53" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6690,28 +6947,28 @@
       <c r="A54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="43">
+      <c r="B54" s="39">
         <v>45959</v>
       </c>
       <c r="C54" s="7">
         <v>45967</v>
       </c>
-      <c r="D54" s="80">
+      <c r="D54" s="22">
         <v>135157735</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="17">
         <v>3450126273</v>
       </c>
-      <c r="F54" s="77" t="s">
+      <c r="F54" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G54" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I54" s="83">
+      <c r="I54" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6719,28 +6976,28 @@
       <c r="A55" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="43">
+      <c r="B55" s="39">
         <v>45959</v>
       </c>
       <c r="C55" s="7">
         <v>45967</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="22">
         <v>135159289</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="17">
         <v>3450126450</v>
       </c>
-      <c r="F55" s="77" t="s">
+      <c r="F55" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="G55" s="24" t="s">
+      <c r="G55" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H55" s="13" t="s">
+      <c r="H55" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I55" s="83">
+      <c r="I55" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6748,28 +7005,28 @@
       <c r="A56" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="43">
+      <c r="B56" s="39">
         <v>45959</v>
       </c>
       <c r="C56" s="7">
         <v>45967</v>
       </c>
-      <c r="D56" s="80">
+      <c r="D56" s="22">
         <v>135164300</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="17">
         <v>3450125404</v>
       </c>
-      <c r="F56" s="77" t="s">
+      <c r="F56" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="G56" s="24" t="s">
+      <c r="G56" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I56" s="83">
+      <c r="I56" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6777,28 +7034,28 @@
       <c r="A57" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B57" s="43">
+      <c r="B57" s="39">
         <v>45959</v>
       </c>
       <c r="C57" s="7">
         <v>45967</v>
       </c>
-      <c r="D57" s="80">
+      <c r="D57" s="22">
         <v>135164486</v>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="17">
         <v>3450126317</v>
       </c>
-      <c r="F57" s="77" t="s">
+      <c r="F57" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="G57" s="24" t="s">
+      <c r="G57" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I57" s="83">
+      <c r="I57" s="77">
         <v>45959</v>
       </c>
     </row>
@@ -6823,17 +7080,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" customWidth="1"/>
     <col min="8" max="8" width="24.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6869,491 +7126,1247 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C2" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D2" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="87">
+        <v>3450127373</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="34"/>
+      <c r="B3" s="7">
+        <v>45962</v>
+      </c>
+      <c r="C3" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D3" s="88" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="88">
+        <v>3450130871</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45911</v>
+      </c>
+      <c r="C4" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D4" s="92" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="92">
+        <v>3450138296</v>
+      </c>
+      <c r="F4" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45954</v>
+      </c>
+      <c r="C5" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D5" s="93">
+        <v>135102201</v>
+      </c>
+      <c r="E5" s="93">
+        <v>3450121224</v>
+      </c>
+      <c r="F5" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="39">
+        <v>45954</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="25"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C6" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D6" s="93">
+        <v>135123518</v>
+      </c>
+      <c r="E6" s="93">
+        <v>3450123138</v>
+      </c>
+      <c r="F6" s="91" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="94" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" s="39">
+        <v>45959</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C7" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D7" s="93">
+        <v>135114020</v>
+      </c>
+      <c r="E7" s="93">
+        <v>3450122027</v>
+      </c>
+      <c r="F7" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="39">
+        <v>45959</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C8" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D8" s="93">
+        <v>135170165</v>
+      </c>
+      <c r="E8" s="93">
+        <v>3450127329</v>
+      </c>
+      <c r="F8" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C9" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D9" s="93">
+        <v>135171770</v>
+      </c>
+      <c r="E9" s="93">
+        <v>3450127461</v>
+      </c>
+      <c r="F9" s="91" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C10" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D10" s="93">
+        <v>135181015</v>
+      </c>
+      <c r="E10" s="93">
+        <v>3450128451</v>
+      </c>
+      <c r="F10" s="91" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C11" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D11" s="93">
+        <v>135172614</v>
+      </c>
+      <c r="E11" s="93">
+        <v>3450127615</v>
+      </c>
+      <c r="F11" s="91" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C12" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D12" s="93">
+        <v>135186149</v>
+      </c>
+      <c r="E12" s="93">
+        <v>3450127901</v>
+      </c>
+      <c r="F12" s="91" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="94" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" s="39">
+        <v>45968</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C13" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D13" s="93">
+        <v>135191534</v>
+      </c>
+      <c r="E13" s="93">
+        <v>3450129199</v>
+      </c>
+      <c r="F13" s="91" t="s">
+        <v>236</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I13" s="39">
+        <v>45967</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C14" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D14" s="93">
+        <v>135185493</v>
+      </c>
+      <c r="E14" s="93">
+        <v>3450127373</v>
+      </c>
+      <c r="F14" s="91" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I14" s="39">
+        <v>45967</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C15" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D15" s="93">
+        <v>135211786</v>
+      </c>
+      <c r="E15" s="93">
+        <v>3450131410</v>
+      </c>
+      <c r="F15" s="91" t="s">
+        <v>239</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I15" s="39">
+        <v>45967</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C16" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D16" s="93">
+        <v>135191074</v>
+      </c>
+      <c r="E16" s="93">
+        <v>3450129089</v>
+      </c>
+      <c r="F16" s="91" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="94" t="s">
+        <v>241</v>
+      </c>
+      <c r="I16" s="39">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C17" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D17" s="93">
+        <v>135245695</v>
+      </c>
+      <c r="E17" s="93">
+        <v>3450134831</v>
+      </c>
+      <c r="F17" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I17" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C18" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D18" s="93">
+        <v>135169298</v>
+      </c>
+      <c r="E18" s="93">
+        <v>3450127197</v>
+      </c>
+      <c r="F18" s="91" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C19" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D19" s="93">
+        <v>135262875</v>
+      </c>
+      <c r="E19" s="93">
+        <v>3450136173</v>
+      </c>
+      <c r="F19" s="91" t="s">
+        <v>244</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I19" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45974</v>
+      </c>
+      <c r="C20" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D20" s="93">
+        <v>135260735</v>
+      </c>
+      <c r="E20" s="93">
+        <v>3450136008</v>
+      </c>
+      <c r="F20" s="91" t="s">
+        <v>245</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="I20" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C21" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D21" s="93">
+        <v>135186289</v>
+      </c>
+      <c r="E21" s="93">
+        <v>3450128132</v>
+      </c>
+      <c r="F21" s="91" t="s">
+        <v>246</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="94" t="s">
+        <v>247</v>
+      </c>
+      <c r="I21" s="39">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C22" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D22" s="93">
+        <v>135276707</v>
+      </c>
+      <c r="E22" s="93">
+        <v>3450137449</v>
+      </c>
+      <c r="F22" s="91" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C23" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D23" s="93">
+        <v>135286641</v>
+      </c>
+      <c r="E23" s="93">
+        <v>3450138340</v>
+      </c>
+      <c r="F23" s="91" t="s">
+        <v>249</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45957</v>
+      </c>
+      <c r="C24" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D24" s="93">
+        <v>135109372</v>
+      </c>
+      <c r="E24" s="93">
+        <v>3450121400</v>
+      </c>
+      <c r="F24" s="91" t="s">
+        <v>250</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="94" t="s">
+        <v>251</v>
+      </c>
+      <c r="I24" s="39">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C25" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D25" s="93">
+        <v>135119133</v>
+      </c>
+      <c r="E25" s="93">
+        <v>3450122533</v>
+      </c>
+      <c r="F25" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="94" t="s">
+        <v>253</v>
+      </c>
+      <c r="I25" s="39">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45957</v>
+      </c>
+      <c r="C26" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D26" s="93">
+        <v>135121726</v>
+      </c>
+      <c r="E26" s="93">
+        <v>3450122841</v>
+      </c>
+      <c r="F26" s="91" t="s">
+        <v>254</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="94" t="s">
+        <v>255</v>
+      </c>
+      <c r="I26" s="39">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45962</v>
+      </c>
+      <c r="C27" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D27" s="93">
+        <v>135198264</v>
+      </c>
+      <c r="E27" s="93">
+        <v>3450130024</v>
+      </c>
+      <c r="F27" s="91" t="s">
+        <v>256</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="94" t="s">
+        <v>237</v>
+      </c>
+      <c r="I27" s="39">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C28" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D28" s="93">
+        <v>135183640</v>
+      </c>
+      <c r="E28" s="93">
+        <v>3450128583</v>
+      </c>
+      <c r="F28" s="91" t="s">
+        <v>257</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="94" t="s">
+        <v>258</v>
+      </c>
+      <c r="I28" s="39">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C29" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D29" s="93">
+        <v>135168728</v>
+      </c>
+      <c r="E29" s="93">
+        <v>3450127164</v>
+      </c>
+      <c r="F29" s="91" t="s">
+        <v>259</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C30" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D30" s="93">
+        <v>135172468</v>
+      </c>
+      <c r="E30" s="93">
+        <v>3450127593</v>
+      </c>
+      <c r="F30" s="91" t="s">
+        <v>260</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C31" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D31" s="93">
+        <v>135172922</v>
+      </c>
+      <c r="E31" s="93">
+        <v>3450127692</v>
+      </c>
+      <c r="F31" s="91" t="s">
+        <v>261</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C32" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D32" s="93">
+        <v>135173613</v>
+      </c>
+      <c r="E32" s="93">
+        <v>3450127791</v>
+      </c>
+      <c r="F32" s="91" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C33" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D33" s="93">
+        <v>135174178</v>
+      </c>
+      <c r="E33" s="93">
+        <v>3450127846</v>
+      </c>
+      <c r="F33" s="91" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C34" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D34" s="93">
+        <v>135176096</v>
+      </c>
+      <c r="E34" s="93">
+        <v>3450127956</v>
+      </c>
+      <c r="F34" s="91" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C35" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D35" s="93">
+        <v>135179982</v>
+      </c>
+      <c r="E35" s="93">
+        <v>3450128319</v>
+      </c>
+      <c r="F35" s="91" t="s">
+        <v>265</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C36" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D36" s="93">
+        <v>135180377</v>
+      </c>
+      <c r="E36" s="93">
+        <v>3450128341</v>
+      </c>
+      <c r="F36" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C37" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D37" s="93">
+        <v>135180081</v>
+      </c>
+      <c r="E37" s="93">
+        <v>3450128320</v>
+      </c>
+      <c r="F37" s="91" t="s">
+        <v>266</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C38" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D38" s="93">
+        <v>135180853</v>
+      </c>
+      <c r="E38" s="93">
+        <v>3450128430</v>
+      </c>
+      <c r="F38" s="91" t="s">
+        <v>232</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="39">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C39" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D39" s="93">
+        <v>135181489</v>
+      </c>
+      <c r="E39" s="93">
+        <v>3450128517</v>
+      </c>
+      <c r="F39" s="91" t="s">
+        <v>267</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C40" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D40" s="93">
+        <v>135181844</v>
+      </c>
+      <c r="E40" s="93">
+        <v>3450128550</v>
+      </c>
+      <c r="F40" s="91" t="s">
+        <v>268</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C41" s="25">
+        <v>45968</v>
+      </c>
+      <c r="D41" s="93">
+        <v>135218972</v>
+      </c>
+      <c r="E41" s="93">
+        <v>3450132411</v>
+      </c>
+      <c r="F41" s="91" t="s">
+        <v>269</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="I41" s="39">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C42" s="95">
+        <v>45968</v>
+      </c>
+      <c r="D42" s="93">
+        <v>135180464</v>
+      </c>
+      <c r="E42" s="93">
+        <v>3450128374</v>
+      </c>
+      <c r="F42" s="91" t="s">
+        <v>271</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="39">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="B43" s="7"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="93"/>
+      <c r="E43" s="93"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="39"/>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="6"/>
       <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="C44" s="25"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="91"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="17"/>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="6"/>
       <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="C45" s="25"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="17"/>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="6"/>
       <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="C46" s="25"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="17"/>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="6"/>
       <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="C47" s="25"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="17"/>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="6"/>
       <c r="B48" s="8"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="14"/>
       <c r="G48" s="6"/>
       <c r="H48" s="9"/>
     </row>
@@ -7397,17 +8410,57 @@
       <c r="G52" s="6"/>
       <c r="H52" s="9"/>
     </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="6"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="9"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="6"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="6"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="9"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="6"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="9"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A56" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -7417,18 +8470,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="16" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7453,7 +8506,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -7464,233 +8517,325 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C2" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D2" s="93">
+        <v>135143631</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450124953</v>
+      </c>
+      <c r="F2" s="91" t="s">
+        <v>272</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="98" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C3" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D3" s="93">
+        <v>135213647</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450131806</v>
+      </c>
+      <c r="F3" s="91" t="s">
+        <v>274</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="96" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="39">
+        <v>45964</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C4" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D4" s="93">
+        <v>135134061</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450123908</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="96" t="s">
+        <v>277</v>
+      </c>
+      <c r="I4" s="39">
+        <v>45971</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="25"/>
+      <c r="B5" s="7">
+        <v>45957</v>
+      </c>
+      <c r="C5" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D5" s="93">
+        <v>135124368</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450123182</v>
+      </c>
+      <c r="F5" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="96" t="s">
+        <v>279</v>
+      </c>
+      <c r="I5" s="39">
+        <v>45957</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="25"/>
+      <c r="B6" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C6" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D6" s="93">
+        <v>135132584</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450123611</v>
+      </c>
+      <c r="F6" s="91" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="I6" s="39">
+        <v>45960</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="25"/>
+      <c r="B7" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C7" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D7" s="93">
+        <v>135138425</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450124326</v>
+      </c>
+      <c r="F7" s="91" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="I7" s="39">
+        <v>45969</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="25"/>
+      <c r="B8" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C8" s="25">
+        <v>45969</v>
+      </c>
+      <c r="D8" s="93">
+        <v>135212565</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450131553</v>
+      </c>
+      <c r="F8" s="91" t="s">
+        <v>284</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="96" t="s">
+        <v>285</v>
+      </c>
+      <c r="I8" s="39">
+        <v>45964</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="25"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="24"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1">
+      <c r="A12" s="26"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="25"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="25"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="25"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="24"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="25"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="30"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="29"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -7698,10 +8843,10 @@
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="30"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="25"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -7710,9 +8855,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="30"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -7721,9 +8866,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="30"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="25"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -7732,9 +8877,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="30"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="25"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -7743,9 +8888,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="30"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="25"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -7756,7 +8901,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="25"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -7767,7 +8912,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="25"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -7778,7 +8923,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="25"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -7789,7 +8934,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="25"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -7800,7 +8945,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="25"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -7811,7 +8956,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="25"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -7822,7 +8967,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="25"/>
+      <c r="I31"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -7833,7 +8978,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="25"/>
+      <c r="I32"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -7844,7 +8989,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="25"/>
+      <c r="I33"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -7855,7 +9000,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="25"/>
+      <c r="I34"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -7866,7 +9011,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="25"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -8033,72 +9178,17 @@
       <c r="H50" s="9"/>
       <c r="I50"/>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A13" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8151,9 +9241,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="8"/>
@@ -8163,232 +9251,198 @@
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="100"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="6"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="6"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="6"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="6"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
     </row>
@@ -8398,7 +9452,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
     </row>
@@ -8772,6 +9826,56 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -8779,7 +9883,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517946</_dlc_DocId>
@@ -8822,9 +9926,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41fed91b93125e9eb81167fcc17a074a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b37f844e38ab5d6be06af21bb96d53eb" ns1:_="" ns2:_="" ns3:_="">
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="942937e371c73d54738c2111de006841">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ef92847a523075df09a9e36a469a0b2" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -8873,12 +9977,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -8887,12 +9991,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -8975,7 +10079,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8994,7 +10098,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -9027,7 +10131,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -9110,8 +10214,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -9200,68 +10304,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8C0D9C2-4E68-45AE-8716-787772E9A414}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{860FACB1-A316-487E-8381-285BE78D7551}"/>
 </file>